--- a/survey/references/OD_nationale_quebec_2025.xlsx
+++ b/survey/references/OD_nationale_quebec_2025.xlsx
@@ -1878,16 +1878,65 @@
     <t xml:space="preserve">Custom because it is a map around the home</t>
   </si>
   <si>
-    <t xml:space="preserve">householdLongDistanceTripsSeptemberDecember</t>
-  </si>
-  <si>
-    <t xml:space="preserve">household.longDistanceTripsSeptemberDecember</t>
-  </si>
-  <si>
-    <t xml:space="preserve">À quelle fréquence vous ou un des membres de votre ménage avez-vous effectué des déplacements longue distance (plus de 40 km) de **septembre à décembre 2024**?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How often did you or a member of your household make long-distance trips (more than 40 km) between **September and December 2024**?</t>
+    <t xml:space="preserve">householdLongDistanceTripsMayAugust</t>
+  </si>
+  <si>
+    <t xml:space="preserve">household.longDistanceTripsMayAugust</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À quelle fréquence vous ou un des membres de votre ménage avez-vous effectué des déplacements longue distance (plus de 40 km) de **mai à août 2026**?</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">How often did you or a member of your household make long-distance trips (more than 40 km) between **</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">May</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">August</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 2026**?</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1918,11 +1967,60 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> de **septembre à décembre 2024**?</t>
+      <t xml:space="preserve"> de **mai à août 2026**?</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">How often did you make long-distance trips (more than 40 km) between **September and December 2024**?</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">How often did you make long-distance trips (more than 40 km) between **</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">May</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">August</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 2026**?</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">madeLongDistanceTripsConditional</t>
@@ -1937,7 +2035,7 @@
     <t xml:space="preserve">household.longDistanceTripsJanuaryApril</t>
   </si>
   <si>
-    <t xml:space="preserve">À quelle fréquence vous ou un des membres de votre ménage avez-vous effectué des déplacements longue distance (plus de 40 km) de **janvier à avril 2025**?</t>
+    <t xml:space="preserve">À quelle fréquence vous ou un des membres de votre ménage avez-vous effectué des déplacements longue distance (plus de 40 km) de **janvier à avril 2026**?</t>
   </si>
   <si>
     <r>
@@ -1988,7 +2086,7 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> 2025**?</t>
+      <t xml:space="preserve"> 2026**?</t>
     </r>
   </si>
   <si>
@@ -2020,7 +2118,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> de **janvier à avril 2025**?</t>
+      <t xml:space="preserve"> de **janvier à avril 2026**?</t>
     </r>
   </si>
   <si>
@@ -2072,69 +2170,20 @@
         <family val="3"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> 2025**?</t>
+      <t xml:space="preserve"> 2026**?</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">householdLongDistanceTripsMayAugust</t>
-  </si>
-  <si>
-    <t xml:space="preserve">household.longDistanceTripsMayAugust</t>
-  </si>
-  <si>
-    <t xml:space="preserve">À quelle fréquence vous ou un des membres de votre ménage avez-vous effectué des déplacements longue distance (plus de 40 km) de **mai à août 2025**?</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">How often did you or a member of your household make long-distance trips (more than 40 km) between **</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">May</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">August</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> 2025**?</t>
-    </r>
+    <t xml:space="preserve">householdLongDistanceTripsSeptemberDecember</t>
+  </si>
+  <si>
+    <t xml:space="preserve">household.longDistanceTripsSeptemberDecember</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À quelle fréquence vous ou un des membres de votre ménage avez-vous effectué des déplacements longue distance (plus de 40 km) de **septembre à décembre 2025**?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How often did you or a member of your household make long-distance trips (more than 40 km) between **September and December 2025**?</t>
   </si>
   <si>
     <r>
@@ -2165,60 +2214,11 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> de **mai à août 2025**?</t>
+      <t xml:space="preserve"> de **septembre à décembre 2025**?</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">How often did you make long-distance trips (more than 40 km) between **</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">May</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">August</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> 2025**?</t>
-    </r>
+    <t xml:space="preserve">How often did you make long-distance trips (more than 40 km) between **September and December 2025**?</t>
   </si>
   <si>
     <t xml:space="preserve">wouldLikeToParticipateToLongDistanceSurvey</t>
@@ -11470,6 +11470,33 @@
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
+      <c r="XED113" s="0"/>
+      <c r="XEE113" s="0"/>
+      <c r="XEF113" s="0"/>
+      <c r="XEG113" s="0"/>
+      <c r="XEH113" s="0"/>
+      <c r="XEI113" s="0"/>
+      <c r="XEJ113" s="0"/>
+      <c r="XEK113" s="0"/>
+      <c r="XEL113" s="0"/>
+      <c r="XEM113" s="0"/>
+      <c r="XEN113" s="0"/>
+      <c r="XEO113" s="0"/>
+      <c r="XEP113" s="0"/>
+      <c r="XEQ113" s="0"/>
+      <c r="XER113" s="0"/>
+      <c r="XES113" s="0"/>
+      <c r="XET113" s="0"/>
+      <c r="XEU113" s="0"/>
+      <c r="XEV113" s="0"/>
+      <c r="XEW113" s="0"/>
+      <c r="XEX113" s="0"/>
+      <c r="XEY113" s="0"/>
+      <c r="XEZ113" s="0"/>
+      <c r="XFA113" s="0"/>
+      <c r="XFB113" s="0"/>
+      <c r="XFC113" s="0"/>
+      <c r="XFD113" s="0"/>
     </row>
     <row r="114" s="2" customFormat="true" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="40" t="s">
@@ -11644,7 +11671,7 @@
       <c r="P117" s="30"/>
       <c r="Q117" s="30"/>
       <c r="R117" s="30"/>
-      <c r="S117" s="28" t="n">
+      <c r="S117" s="28" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -12407,6 +12434,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <autoFilter ref="A1:W1"/>

--- a/survey/references/OD_nationale_quebec_2025.xlsx
+++ b/survey/references/OD_nationale_quebec_2025.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="1469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2450" uniqueCount="1469">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -439,7 +439,10 @@
     <t xml:space="preserve">**Permanent physical, intellectual or other disability** which influences or limits your daily mobility?</t>
   </si>
   <si>
-    <t xml:space="preserve">hasOnePersonWithDisabilityOrHhSize1Conditional</t>
+    <t xml:space="preserve">hasOnePersonWithDisabilityOrHhSize1CustomConditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom conditional because the generator does not support values when hidden that can be paths in the interview</t>
   </si>
   <si>
     <t xml:space="preserve">personSexAssignedAtBirth</t>
@@ -2762,67 +2765,64 @@
     <t xml:space="preserve">&gt;=</t>
   </si>
   <si>
-    <t xml:space="preserve">household.atLeastOnePersonWithDisability</t>
+    <t xml:space="preserve">household.bicycleNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${currentPerson}.sexAssignedAtBirth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preferNotToAnswer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ifAge3to5Conditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${currentPerson}.age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&amp;&amp;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;=</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ifAge4to13Conditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ifAge4to15Conditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ifAge5OrLessConditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ifAge11OrMoreConditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!==</t>
+  </si>
+  <si>
+    <t xml:space="preserve">null</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ifAge16OrLessConditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ifAge40OrMoreConditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">${currentPerson}.drivingLicenseOwnership</t>
   </si>
   <si>
     <t xml:space="preserve">yes</t>
   </si>
   <si>
+    <t xml:space="preserve">${currentPerson}.occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fullTimeWorker</t>
+  </si>
+  <si>
     <t xml:space="preserve">||</t>
-  </si>
-  <si>
-    <t xml:space="preserve">household.bicycleNumber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${currentPerson}.sexAssignedAtBirth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">preferNotToAnswer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ifAge3to5Conditional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${currentPerson}.age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;&amp;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;=</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ifAge4to13Conditional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ifAge4to15Conditional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ifAge5OrLessConditional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ifAge11OrMoreConditional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!==</t>
-  </si>
-  <si>
-    <t xml:space="preserve">null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ifAge16OrLessConditional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ifAge40OrMoreConditional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${currentPerson}.drivingLicenseOwnership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">${currentPerson}.occupation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fullTimeWorker</t>
   </si>
   <si>
     <t xml:space="preserve">partTimeWorker</t>
@@ -7308,7 +7308,7 @@
       <c r="V21" s="20"/>
       <c r="W21" s="20"/>
     </row>
-    <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="18" t="s">
         <v>122</v>
       </c>
@@ -7360,10 +7360,13 @@
       <c r="U22" s="20"/>
       <c r="V22" s="20"/>
       <c r="W22" s="20"/>
+      <c r="X22" s="1" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B23" s="18" t="s">
         <v>33</v>
@@ -7379,24 +7382,24 @@
         <v>106</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
       <c r="K23" s="18"/>
       <c r="L23" s="20"/>
       <c r="M23" s="20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N23" s="20"/>
       <c r="O23" s="20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P23" s="20"/>
       <c r="Q23" s="20"/>
@@ -7412,7 +7415,7 @@
     </row>
     <row r="24" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B24" s="18" t="s">
         <v>33</v>
@@ -7428,24 +7431,24 @@
         <v>106</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
       <c r="K24" s="18"/>
       <c r="L24" s="20"/>
       <c r="M24" s="20" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N24" s="20"/>
       <c r="O24" s="20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P24" s="20"/>
       <c r="Q24" s="20"/>
@@ -7455,20 +7458,20 @@
         <v>1</v>
       </c>
       <c r="T24" s="20" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="U24" s="20" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="V24" s="20"/>
       <c r="W24" s="20"/>
       <c r="X24" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>33</v>
@@ -7484,24 +7487,24 @@
         <v>106</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I25" s="18"/>
       <c r="J25" s="18"/>
       <c r="K25" s="18"/>
       <c r="L25" s="20"/>
       <c r="M25" s="20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N25" s="20"/>
       <c r="O25" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P25" s="20"/>
       <c r="Q25" s="20"/>
@@ -7517,7 +7520,7 @@
     </row>
     <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B26" s="18" t="s">
         <v>33</v>
@@ -7533,24 +7536,24 @@
         <v>106</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
       <c r="K26" s="18"/>
       <c r="L26" s="20"/>
       <c r="M26" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N26" s="20"/>
       <c r="O26" s="20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P26" s="21"/>
       <c r="Q26" s="20"/>
@@ -7566,7 +7569,7 @@
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B27" s="18" t="s">
         <v>72</v>
@@ -7582,24 +7585,24 @@
         <v>106</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I27" s="18"/>
       <c r="J27" s="18"/>
       <c r="K27" s="18"/>
       <c r="L27" s="20"/>
       <c r="M27" s="22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N27" s="20"/>
       <c r="O27" s="20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P27" s="20"/>
       <c r="Q27" s="20"/>
@@ -7609,17 +7612,17 @@
         <v>1</v>
       </c>
       <c r="T27" s="20" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="U27" s="20" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="V27" s="20"/>
       <c r="W27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="18" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B28" s="18" t="s">
         <v>33</v>
@@ -7635,24 +7638,24 @@
         <v>106</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I28" s="18"/>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
       <c r="L28" s="20"/>
       <c r="M28" s="20" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N28" s="20"/>
       <c r="O28" s="20" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P28" s="20"/>
       <c r="Q28" s="20"/>
@@ -7668,7 +7671,7 @@
     </row>
     <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B29" s="18" t="s">
         <v>33</v>
@@ -7684,28 +7687,28 @@
         <v>106</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I29" s="18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K29" s="18"/>
       <c r="L29" s="20"/>
       <c r="M29" s="20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N29" s="20"/>
       <c r="O29" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P29" s="20"/>
       <c r="Q29" s="20"/>
@@ -7721,7 +7724,7 @@
     </row>
     <row r="30" customFormat="false" ht="45.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B30" s="18" t="s">
         <v>33</v>
@@ -7737,24 +7740,24 @@
         <v>106</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I30" s="18"/>
       <c r="J30" s="18"/>
       <c r="K30" s="18"/>
       <c r="L30" s="20"/>
       <c r="M30" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N30" s="20"/>
       <c r="O30" s="23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P30" s="20"/>
       <c r="Q30" s="20"/>
@@ -7770,7 +7773,7 @@
     </row>
     <row r="31" customFormat="false" ht="62.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B31" s="18" t="s">
         <v>33</v>
@@ -7786,24 +7789,24 @@
         <v>106</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I31" s="18"/>
       <c r="J31" s="18"/>
       <c r="K31" s="18"/>
       <c r="L31" s="20"/>
       <c r="M31" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N31" s="20"/>
       <c r="O31" s="20" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P31" s="20"/>
       <c r="Q31" s="20"/>
@@ -7819,7 +7822,7 @@
     </row>
     <row r="32" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B32" s="18" t="s">
         <v>33</v>
@@ -7835,24 +7838,24 @@
         <v>106</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I32" s="18"/>
       <c r="J32" s="18"/>
       <c r="K32" s="18"/>
       <c r="L32" s="20"/>
       <c r="M32" s="20" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N32" s="20"/>
       <c r="O32" s="20" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P32" s="20"/>
       <c r="Q32" s="20"/>
@@ -7868,10 +7871,10 @@
     </row>
     <row r="33" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C33" s="18" t="b">
         <f aca="false">TRUE()</f>
@@ -7884,30 +7887,30 @@
         <v>106</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I33" s="18" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J33" s="18" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K33" s="18"/>
       <c r="L33" s="20"/>
       <c r="M33" s="20" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N33" s="20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O33" s="20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P33" s="20"/>
       <c r="Q33" s="20"/>
@@ -7923,7 +7926,7 @@
     </row>
     <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B34" s="18" t="s">
         <v>33</v>
@@ -7939,28 +7942,28 @@
         <v>106</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J34" s="18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K34" s="18"/>
       <c r="L34" s="20"/>
       <c r="M34" s="20" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N34" s="20"/>
       <c r="O34" s="20" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P34" s="20"/>
       <c r="Q34" s="20"/>
@@ -7976,7 +7979,7 @@
     </row>
     <row r="35" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B35" s="18" t="s">
         <v>33</v>
@@ -7992,28 +7995,28 @@
         <v>106</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I35" s="18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J35" s="18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K35" s="18"/>
       <c r="L35" s="20"/>
       <c r="M35" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N35" s="20"/>
       <c r="O35" s="20" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P35" s="20"/>
       <c r="Q35" s="20"/>
@@ -8029,7 +8032,7 @@
     </row>
     <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B36" s="18" t="s">
         <v>33</v>
@@ -8045,28 +8048,28 @@
         <v>106</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I36" s="18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J36" s="18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K36" s="18"/>
       <c r="L36" s="20"/>
       <c r="M36" s="20" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N36" s="20"/>
       <c r="O36" s="20" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P36" s="20"/>
       <c r="Q36" s="20"/>
@@ -8082,7 +8085,7 @@
     </row>
     <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B37" s="18" t="s">
         <v>25</v>
@@ -8098,26 +8101,26 @@
         <v>106</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I37" s="18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J37" s="18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K37" s="2"/>
       <c r="L37" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M37" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N37" s="20"/>
       <c r="O37" s="20"/>
@@ -8135,7 +8138,7 @@
     </row>
     <row r="38" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B38" s="25" t="s">
         <v>72</v>
@@ -8151,24 +8154,24 @@
         <v>106</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I38" s="18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J38" s="18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K38" s="18"/>
       <c r="L38" s="20"/>
       <c r="M38" s="18" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N38" s="20"/>
       <c r="O38" s="20"/>
@@ -8186,7 +8189,7 @@
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B39" s="18" t="s">
         <v>25</v>
@@ -8202,26 +8205,26 @@
         <v>106</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I39" s="18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J39" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K39" s="2"/>
       <c r="L39" s="18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M39" s="18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N39" s="20"/>
       <c r="O39" s="20"/>
@@ -8239,7 +8242,7 @@
     </row>
     <row r="40" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B40" s="25" t="s">
         <v>72</v>
@@ -8255,19 +8258,19 @@
         <v>106</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J40" s="18" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K40" s="26"/>
       <c r="L40" s="27"/>
@@ -8288,10 +8291,10 @@
     </row>
     <row r="41" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C41" s="18" t="n">
         <f aca="false">TRUE()</f>
@@ -8304,30 +8307,30 @@
         <v>106</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I41" s="18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J41" s="18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K41" s="18"/>
       <c r="L41" s="20"/>
       <c r="M41" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O41" s="20" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P41" s="20"/>
       <c r="Q41" s="20"/>
@@ -8343,10 +8346,10 @@
     </row>
     <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="18" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C42" s="18" t="n">
         <f aca="false">TRUE()</f>
@@ -8359,30 +8362,30 @@
         <v>106</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I42" s="18" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J42" s="18" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K42" s="18"/>
       <c r="L42" s="20"/>
       <c r="M42" s="20" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N42" s="20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O42" s="20" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P42" s="20"/>
       <c r="Q42" s="20"/>
@@ -8398,7 +8401,7 @@
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="28" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B43" s="28" t="s">
         <v>103</v>
@@ -8431,7 +8434,7 @@
       <c r="P43" s="30"/>
       <c r="Q43" s="30"/>
       <c r="R43" s="30" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="S43" s="28" t="b">
         <f aca="false">TRUE()</f>
@@ -8444,7 +8447,7 @@
     </row>
     <row r="44" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B44" s="28" t="s">
         <v>72</v>
@@ -8454,17 +8457,17 @@
         <v>1</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E44" s="30"/>
       <c r="F44" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I44" s="28"/>
       <c r="J44" s="28"/>
@@ -8484,7 +8487,7 @@
     </row>
     <row r="45" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B45" s="28" t="s">
         <v>103</v>
@@ -8494,17 +8497,17 @@
         <v>1</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E45" s="10"/>
       <c r="F45" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I45" s="28"/>
       <c r="J45" s="28"/>
@@ -8524,27 +8527,27 @@
     </row>
     <row r="46" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C46" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D46" s="28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E46" s="30"/>
       <c r="F46" s="30" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H46" s="32" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I46" s="28"/>
       <c r="J46" s="28"/>
@@ -8570,27 +8573,27 @@
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B47" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C47" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E47" s="30"/>
       <c r="F47" s="30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G47" s="28" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H47" s="28" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I47" s="28"/>
       <c r="J47" s="28"/>
@@ -8610,7 +8613,7 @@
     </row>
     <row r="48" customFormat="false" ht="226.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B48" s="28" t="s">
         <v>72</v>
@@ -8620,17 +8623,17 @@
         <v>1</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E48" s="30"/>
       <c r="F48" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I48" s="28"/>
       <c r="J48" s="28"/>
@@ -8650,7 +8653,7 @@
     </row>
     <row r="49" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B49" s="28" t="s">
         <v>72</v>
@@ -8660,17 +8663,17 @@
         <v>1</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E49" s="30"/>
       <c r="F49" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I49" s="28"/>
       <c r="J49" s="28"/>
@@ -8690,7 +8693,7 @@
     </row>
     <row r="50" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B50" s="28" t="s">
         <v>72</v>
@@ -8700,23 +8703,23 @@
         <v>1</v>
       </c>
       <c r="D50" s="28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E50" s="30"/>
       <c r="F50" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J50" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K50" s="28"/>
       <c r="L50" s="30"/>
@@ -8734,7 +8737,7 @@
     </row>
     <row r="51" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B51" s="28" t="s">
         <v>72</v>
@@ -8744,23 +8747,23 @@
         <v>1</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E51" s="30"/>
       <c r="F51" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K51" s="28"/>
       <c r="L51" s="30"/>
@@ -8778,7 +8781,7 @@
     </row>
     <row r="52" customFormat="false" ht="404.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B52" s="28" t="s">
         <v>72</v>
@@ -8788,23 +8791,23 @@
         <v>1</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E52" s="30"/>
       <c r="F52" s="30" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K52" s="28"/>
       <c r="L52" s="30"/>
@@ -8822,7 +8825,7 @@
     </row>
     <row r="53" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B53" s="28" t="s">
         <v>72</v>
@@ -8832,23 +8835,23 @@
         <v>1</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E53" s="30"/>
       <c r="F53" s="30" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K53" s="28"/>
       <c r="L53" s="30"/>
@@ -8866,7 +8869,7 @@
     </row>
     <row r="54" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B54" s="28" t="s">
         <v>33</v>
@@ -8876,32 +8879,32 @@
         <v>1</v>
       </c>
       <c r="D54" s="28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E54" s="30"/>
       <c r="F54" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K54" s="28"/>
       <c r="L54" s="30"/>
       <c r="M54" s="30" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N54" s="30"/>
       <c r="O54" s="30" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P54" s="30"/>
       <c r="Q54" s="30"/>
@@ -8917,7 +8920,7 @@
     </row>
     <row r="55" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B55" s="28" t="s">
         <v>103</v>
@@ -8927,17 +8930,17 @@
         <v>1</v>
       </c>
       <c r="D55" s="28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E55" s="30"/>
       <c r="F55" s="30" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G55" s="28" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H55" s="28" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I55" s="28"/>
       <c r="J55" s="28"/>
@@ -8957,7 +8960,7 @@
     </row>
     <row r="56" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B56" s="28" t="s">
         <v>38</v>
@@ -8967,17 +8970,17 @@
         <v>1</v>
       </c>
       <c r="D56" s="28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E56" s="30"/>
       <c r="F56" s="30" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H56" s="34" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I56" s="28"/>
       <c r="J56" s="28"/>
@@ -9000,27 +9003,27 @@
     </row>
     <row r="57" s="2" customFormat="true" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B57" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C57" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D57" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E57" s="30"/>
       <c r="F57" s="30" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H57" s="32" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I57" s="28"/>
       <c r="J57" s="28"/>
@@ -9045,27 +9048,27 @@
     </row>
     <row r="58" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B58" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C58" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E58" s="30"/>
       <c r="F58" s="30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G58" s="28" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H58" s="28" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I58" s="28"/>
       <c r="J58" s="28"/>
@@ -9085,33 +9088,33 @@
     </row>
     <row r="59" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="B59" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="C59" s="28" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D59" s="28" t="s">
         <v>332</v>
-      </c>
-      <c r="B59" s="28" t="s">
-        <v>279</v>
-      </c>
-      <c r="C59" s="28" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D59" s="28" t="s">
-        <v>331</v>
       </c>
       <c r="E59" s="30"/>
       <c r="F59" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J59" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K59" s="28"/>
       <c r="L59" s="30"/>
@@ -9132,33 +9135,33 @@
     </row>
     <row r="60" customFormat="false" ht="38.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B60" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C60" s="28" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E60" s="30"/>
       <c r="F60" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J60" s="35" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K60" s="28"/>
       <c r="L60" s="30"/>
@@ -9176,21 +9179,21 @@
     </row>
     <row r="61" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B61" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C61" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D61" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E61" s="30"/>
       <c r="F61" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G61" s="10"/>
       <c r="H61" s="34"/>
@@ -9212,23 +9215,23 @@
     </row>
     <row r="62" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B62" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C62" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D62" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E62" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F62" s="30" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G62" s="10"/>
       <c r="H62" s="34"/>
@@ -9250,23 +9253,23 @@
     </row>
     <row r="63" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B63" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C63" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D63" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E63" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F63" s="30" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G63" s="10"/>
       <c r="H63" s="34"/>
@@ -9288,35 +9291,35 @@
     </row>
     <row r="64" customFormat="false" ht="35.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B64" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C64" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D64" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F64" s="36" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H64" s="34" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J64" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K64" s="28"/>
       <c r="L64" s="30"/>
@@ -9334,40 +9337,40 @@
     </row>
     <row r="65" customFormat="false" ht="69.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B65" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C65" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D65" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E65" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K65" s="28"/>
       <c r="L65" s="30"/>
       <c r="M65" s="30" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N65" s="30"/>
       <c r="O65" s="30" t="s">
@@ -9387,29 +9390,29 @@
     </row>
     <row r="66" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B66" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C66" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D66" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E66" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F66" s="30" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I66" s="28"/>
       <c r="J66" s="28"/>
@@ -9429,23 +9432,23 @@
     </row>
     <row r="67" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B67" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C67" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F67" s="30" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G67" s="10"/>
       <c r="H67" s="34"/>
@@ -9467,29 +9470,29 @@
     </row>
     <row r="68" customFormat="false" ht="150.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B68" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C68" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D68" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E68" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H68" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I68" s="28"/>
       <c r="J68" s="28"/>
@@ -9509,35 +9512,35 @@
     </row>
     <row r="69" customFormat="false" ht="46.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B69" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C69" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D69" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E69" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G69" s="35" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H69" s="35" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I69" s="35" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J69" s="35" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K69" s="28"/>
       <c r="L69" s="30"/>
@@ -9555,35 +9558,35 @@
     </row>
     <row r="70" customFormat="false" ht="40.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B70" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C70" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D70" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E70" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J70" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K70" s="28"/>
       <c r="L70" s="30"/>
@@ -9601,35 +9604,35 @@
     </row>
     <row r="71" customFormat="false" ht="39.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B71" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C71" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D71" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E71" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J71" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K71" s="28"/>
       <c r="L71" s="30"/>
@@ -9647,35 +9650,35 @@
     </row>
     <row r="72" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B72" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C72" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D72" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E72" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F72" s="30" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K72" s="28"/>
       <c r="L72" s="30"/>
@@ -9693,35 +9696,35 @@
     </row>
     <row r="73" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B73" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C73" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D73" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J73" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K73" s="28"/>
       <c r="L73" s="30"/>
@@ -9739,44 +9742,44 @@
     </row>
     <row r="74" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B74" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C74" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D74" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E74" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F74" s="36" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H74" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J74" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K74" s="28"/>
       <c r="L74" s="30"/>
       <c r="M74" s="30" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N74" s="30"/>
       <c r="O74" s="30" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P74" s="30"/>
       <c r="Q74" s="30"/>
@@ -9789,35 +9792,35 @@
     </row>
     <row r="75" customFormat="false" ht="44.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B75" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C75" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D75" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E75" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J75" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K75" s="28"/>
       <c r="L75" s="30"/>
@@ -9835,29 +9838,29 @@
     </row>
     <row r="76" customFormat="false" ht="40.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B76" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C76" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D76" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E76" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F76" s="30" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H76" s="34" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I76" s="28"/>
       <c r="J76" s="28"/>
@@ -9877,20 +9880,20 @@
     </row>
     <row r="77" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B77" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C77" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D77" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E77" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F77" s="30"/>
       <c r="G77" s="10"/>
@@ -9913,20 +9916,20 @@
     </row>
     <row r="78" customFormat="false" ht="41.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B78" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C78" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D78" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E78" s="30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F78" s="30"/>
       <c r="G78" s="10"/>
@@ -9949,34 +9952,34 @@
     </row>
     <row r="79" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B79" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C79" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D79" s="28" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E79" s="30"/>
       <c r="F79" s="30" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I79" s="28"/>
       <c r="J79" s="28"/>
       <c r="K79" s="28"/>
       <c r="L79" s="30"/>
       <c r="M79" s="30" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N79" s="30"/>
       <c r="O79" s="30"/>
@@ -9991,17 +9994,17 @@
     </row>
     <row r="80" s="2" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B80" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C80" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D80" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E80" s="30"/>
       <c r="F80" s="30"/>
@@ -10028,27 +10031,27 @@
     </row>
     <row r="81" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B81" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C81" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E81" s="30"/>
       <c r="F81" s="30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G81" s="28" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H81" s="28" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I81" s="28"/>
       <c r="J81" s="28"/>
@@ -10068,33 +10071,33 @@
     </row>
     <row r="82" customFormat="false" ht="29.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="B82" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="C82" s="28" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="D82" s="28" t="s">
         <v>428</v>
-      </c>
-      <c r="B82" s="28" t="s">
-        <v>279</v>
-      </c>
-      <c r="C82" s="28" t="n">
-        <f aca="false">TRUE()</f>
-        <v>1</v>
-      </c>
-      <c r="D82" s="28" t="s">
-        <v>427</v>
       </c>
       <c r="E82" s="30"/>
       <c r="F82" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J82" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K82" s="28"/>
       <c r="L82" s="30"/>
@@ -10115,33 +10118,33 @@
     </row>
     <row r="83" customFormat="false" ht="38.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B83" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C83" s="28" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D83" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E83" s="30"/>
       <c r="F83" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I83" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J83" s="35" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K83" s="28"/>
       <c r="L83" s="30"/>
@@ -10159,21 +10162,21 @@
     </row>
     <row r="84" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B84" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C84" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D84" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E84" s="30"/>
       <c r="F84" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G84" s="10"/>
       <c r="H84" s="34"/>
@@ -10195,29 +10198,29 @@
     </row>
     <row r="85" customFormat="false" ht="38.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B85" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C85" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D85" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E85" s="30" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="I85" s="28"/>
       <c r="J85" s="28"/>
@@ -10237,29 +10240,29 @@
     </row>
     <row r="86" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B86" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C86" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D86" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E86" s="30" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G86" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H86" s="34" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I86" s="28"/>
       <c r="J86" s="28"/>
@@ -10279,23 +10282,23 @@
     </row>
     <row r="87" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B87" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C87" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D87" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E87" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G87" s="10"/>
       <c r="H87" s="34"/>
@@ -10317,23 +10320,23 @@
     </row>
     <row r="88" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B88" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C88" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D88" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E88" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F88" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G88" s="10"/>
       <c r="H88" s="34"/>
@@ -10355,23 +10358,23 @@
     </row>
     <row r="89" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B89" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C89" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D89" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E89" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G89" s="10"/>
       <c r="H89" s="34"/>
@@ -10393,7 +10396,7 @@
     </row>
     <row r="90" customFormat="false" ht="120.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B90" s="28" t="s">
         <v>72</v>
@@ -10403,25 +10406,25 @@
         <v>1</v>
       </c>
       <c r="D90" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E90" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G90" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H90" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J90" s="14" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K90" s="14"/>
       <c r="L90" s="30"/>
@@ -10437,12 +10440,12 @@
       <c r="V90" s="30"/>
       <c r="W90" s="30"/>
       <c r="X90" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="37.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B91" s="28" t="s">
         <v>33</v>
@@ -10452,30 +10455,30 @@
         <v>1</v>
       </c>
       <c r="D91" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E91" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I91" s="14"/>
       <c r="J91" s="14"/>
       <c r="K91" s="14"/>
       <c r="L91" s="30"/>
       <c r="M91" s="30" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N91" s="30"/>
       <c r="O91" s="30" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P91" s="30"/>
       <c r="Q91" s="30"/>
@@ -10491,7 +10494,7 @@
     </row>
     <row r="92" customFormat="false" ht="32.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B92" s="28" t="s">
         <v>82</v>
@@ -10501,28 +10504,28 @@
         <v>1</v>
       </c>
       <c r="D92" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E92" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H92" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="I92" s="14"/>
       <c r="J92" s="14"/>
       <c r="K92" s="8" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L92" s="30"/>
       <c r="M92" s="30" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N92" s="30"/>
       <c r="O92" s="30"/>
@@ -10540,29 +10543,29 @@
     </row>
     <row r="93" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B93" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C93" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D93" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E93" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G93" s="37" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="I93" s="14"/>
       <c r="J93" s="14"/>
@@ -10585,7 +10588,7 @@
     </row>
     <row r="94" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B94" s="28" t="s">
         <v>72</v>
@@ -10595,19 +10598,19 @@
         <v>1</v>
       </c>
       <c r="D94" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E94" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I94" s="14"/>
       <c r="J94" s="14"/>
@@ -10628,12 +10631,12 @@
       <c r="V94" s="30"/>
       <c r="W94" s="30"/>
       <c r="X94" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="33.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B95" s="28" t="s">
         <v>72</v>
@@ -10643,19 +10646,19 @@
         <v>1</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E95" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I95" s="14"/>
       <c r="J95" s="14"/>
@@ -10676,12 +10679,12 @@
       <c r="V95" s="30"/>
       <c r="W95" s="30"/>
       <c r="X95" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B96" s="28" t="s">
         <v>33</v>
@@ -10691,30 +10694,30 @@
         <v>1</v>
       </c>
       <c r="D96" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E96" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I96" s="14"/>
       <c r="J96" s="14"/>
       <c r="K96" s="14"/>
       <c r="L96" s="30"/>
       <c r="M96" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N96" s="30"/>
       <c r="O96" s="30" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P96" s="30"/>
       <c r="Q96" s="30"/>
@@ -10730,7 +10733,7 @@
     </row>
     <row r="97" customFormat="false" ht="48.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B97" s="28" t="s">
         <v>25</v>
@@ -10740,29 +10743,29 @@
         <v>1</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E97" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I97" s="14"/>
       <c r="J97" s="14"/>
       <c r="K97" s="14"/>
       <c r="L97" s="30"/>
       <c r="M97" s="30" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N97" s="30" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O97" s="30"/>
       <c r="P97" s="30"/>
@@ -10779,7 +10782,7 @@
     </row>
     <row r="98" customFormat="false" ht="39.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B98" s="28" t="s">
         <v>72</v>
@@ -10789,19 +10792,19 @@
         <v>1</v>
       </c>
       <c r="D98" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E98" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="I98" s="14"/>
       <c r="J98" s="14"/>
@@ -10819,25 +10822,25 @@
       <c r="V98" s="30"/>
       <c r="W98" s="30"/>
       <c r="X98" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B99" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C99" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D99" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E99" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F99" s="10"/>
       <c r="G99" s="10"/>
@@ -10860,29 +10863,29 @@
     </row>
     <row r="100" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="10" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B100" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C100" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E100" s="30" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I100" s="14"/>
       <c r="J100" s="14"/>
@@ -10902,34 +10905,34 @@
     </row>
     <row r="101" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="10" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B101" s="28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C101" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D101" s="28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E101" s="30"/>
       <c r="F101" s="30" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="I101" s="14"/>
       <c r="J101" s="14"/>
       <c r="K101" s="14"/>
       <c r="L101" s="30"/>
       <c r="M101" s="30" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N101" s="30"/>
       <c r="O101" s="30"/>
@@ -10944,7 +10947,7 @@
     </row>
     <row r="102" s="2" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B102" s="28" t="s">
         <v>72</v>
@@ -10954,7 +10957,7 @@
         <v>1</v>
       </c>
       <c r="D102" s="28" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E102" s="30"/>
       <c r="F102" s="30"/>
@@ -10979,12 +10982,12 @@
       <c r="V102" s="30"/>
       <c r="W102" s="30"/>
       <c r="X102" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B103" s="28" t="s">
         <v>72</v>
@@ -10994,17 +10997,17 @@
         <v>1</v>
       </c>
       <c r="D103" s="28" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E103" s="30"/>
       <c r="F103" s="30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G103" s="28" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H103" s="28" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I103" s="28"/>
       <c r="J103" s="28"/>
@@ -11022,12 +11025,12 @@
       <c r="V103" s="30"/>
       <c r="W103" s="30"/>
       <c r="X103" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="10" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B104" s="28" t="s">
         <v>72</v>
@@ -11037,17 +11040,17 @@
         <v>1</v>
       </c>
       <c r="D104" s="28" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E104" s="30"/>
       <c r="F104" s="30" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I104" s="14"/>
       <c r="J104" s="14"/>
@@ -11068,45 +11071,45 @@
       <c r="V104" s="30"/>
       <c r="W104" s="30"/>
       <c r="X104" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="10" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B105" s="28" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C105" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D105" s="28" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E105" s="30"/>
       <c r="F105" s="10" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I105" s="14"/>
       <c r="J105" s="14"/>
       <c r="K105" s="14"/>
       <c r="L105" s="30"/>
       <c r="M105" s="30" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N105" s="30" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O105" s="30" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P105" s="30"/>
       <c r="Q105" s="30"/>
@@ -11119,7 +11122,7 @@
     </row>
     <row r="106" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="10" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B106" s="28" t="s">
         <v>72</v>
@@ -11129,31 +11132,31 @@
         <v>1</v>
       </c>
       <c r="D106" s="28" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E106" s="30"/>
       <c r="F106" s="10" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K106" s="14"/>
       <c r="L106" s="30"/>
       <c r="M106" s="30" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N106" s="30" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O106" s="30"/>
       <c r="P106" s="30"/>
@@ -11168,12 +11171,12 @@
       <c r="V106" s="30"/>
       <c r="W106" s="30"/>
       <c r="X106" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="10" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B107" s="28" t="s">
         <v>72</v>
@@ -11183,17 +11186,17 @@
         <v>1</v>
       </c>
       <c r="D107" s="28" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E107" s="30"/>
       <c r="F107" s="30" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I107" s="14"/>
       <c r="J107" s="14"/>
@@ -11214,45 +11217,45 @@
       <c r="V107" s="30"/>
       <c r="W107" s="30"/>
       <c r="X107" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B108" s="28" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C108" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D108" s="28" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E108" s="30"/>
       <c r="F108" s="10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="I108" s="14"/>
       <c r="J108" s="14"/>
       <c r="K108" s="14"/>
       <c r="L108" s="30"/>
       <c r="M108" s="30" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N108" s="30" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="O108" s="30" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P108" s="30"/>
       <c r="Q108" s="30"/>
@@ -11265,7 +11268,7 @@
     </row>
     <row r="109" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="10" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B109" s="28" t="s">
         <v>72</v>
@@ -11275,31 +11278,31 @@
         <v>1</v>
       </c>
       <c r="D109" s="28" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E109" s="30"/>
       <c r="F109" s="10" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="K109" s="2"/>
       <c r="L109" s="30"/>
       <c r="M109" s="30" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N109" s="30" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O109" s="30"/>
       <c r="P109" s="30"/>
@@ -11314,12 +11317,12 @@
       <c r="V109" s="30"/>
       <c r="W109" s="30"/>
       <c r="X109" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B110" s="28" t="s">
         <v>103</v>
@@ -11329,17 +11332,17 @@
         <v>1</v>
       </c>
       <c r="D110" s="28" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E110" s="30"/>
       <c r="F110" s="30" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="G110" s="28" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H110" s="28" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I110" s="30"/>
       <c r="J110" s="30"/>
@@ -11359,7 +11362,7 @@
     </row>
     <row r="111" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B111" s="28" t="s">
         <v>33</v>
@@ -11369,30 +11372,30 @@
         <v>1</v>
       </c>
       <c r="D111" s="35" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E111" s="30"/>
       <c r="F111" s="10" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G111" s="38" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H111" s="38" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I111" s="39" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="J111" s="38" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K111" s="30"/>
       <c r="L111" s="30"/>
       <c r="M111" s="30"/>
       <c r="N111" s="30"/>
       <c r="O111" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P111" s="14"/>
       <c r="Q111" s="30"/>
@@ -11408,7 +11411,7 @@
     </row>
     <row r="112" s="2" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="40" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B112" s="40" t="s">
         <v>72</v>
@@ -11418,7 +11421,7 @@
         <v>1</v>
       </c>
       <c r="D112" s="35" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E112" s="41"/>
       <c r="F112" s="40" t="str">
@@ -11438,12 +11441,12 @@
         <v>1</v>
       </c>
       <c r="X112" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="113" s="2" customFormat="true" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="40" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B113" s="28" t="s">
         <v>33</v>
@@ -11453,32 +11456,32 @@
         <v>1</v>
       </c>
       <c r="D113" s="35" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E113" s="41"/>
       <c r="F113" s="40" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="G113" s="42" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H113" s="44" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I113" s="42" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J113" s="44" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="K113" s="1"/>
       <c r="L113" s="1"/>
       <c r="M113" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N113" s="1"/>
       <c r="O113" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S113" s="14" t="b">
         <f aca="false">TRUE()</f>
@@ -11487,7 +11490,7 @@
     </row>
     <row r="114" s="2" customFormat="true" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="40" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B114" s="28" t="s">
         <v>33</v>
@@ -11497,32 +11500,32 @@
         <v>1</v>
       </c>
       <c r="D114" s="35" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E114" s="41"/>
       <c r="F114" s="40" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G114" s="42" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H114" s="44" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="I114" s="42" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="J114" s="44" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="K114" s="1"/>
       <c r="L114" s="1"/>
       <c r="M114" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N114" s="1"/>
       <c r="O114" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S114" s="14" t="b">
         <f aca="false">TRUE()</f>
@@ -11531,7 +11534,7 @@
     </row>
     <row r="115" s="2" customFormat="true" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="40" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B115" s="28" t="s">
         <v>33</v>
@@ -11541,32 +11544,32 @@
         <v>1</v>
       </c>
       <c r="D115" s="35" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E115" s="41"/>
       <c r="F115" s="40" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="G115" s="42" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H115" s="44" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I115" s="42" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J115" s="44" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="K115" s="1"/>
       <c r="L115" s="1"/>
       <c r="M115" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N115" s="1"/>
       <c r="O115" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="S115" s="14" t="b">
         <f aca="false">TRUE()</f>
@@ -11575,7 +11578,7 @@
     </row>
     <row r="116" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="10" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B116" s="28" t="s">
         <v>33</v>
@@ -11585,24 +11588,24 @@
         <v>1</v>
       </c>
       <c r="D116" s="35" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E116" s="30"/>
       <c r="F116" s="10" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G116" s="45" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H116" s="45" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="I116" s="14"/>
       <c r="J116" s="14"/>
       <c r="K116" s="14"/>
       <c r="L116" s="30"/>
       <c r="M116" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="30" t="s">
@@ -11622,7 +11625,7 @@
     </row>
     <row r="117" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="10" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B117" s="28" t="s">
         <v>25</v>
@@ -11632,27 +11635,27 @@
         <v>1</v>
       </c>
       <c r="D117" s="35" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E117" s="30"/>
       <c r="F117" s="10" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G117" s="45" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H117" s="45" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="I117" s="14"/>
       <c r="J117" s="14"/>
       <c r="K117" s="14"/>
       <c r="L117" s="30"/>
       <c r="M117" s="30" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N117" s="8" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O117" s="30"/>
       <c r="P117" s="30"/>
@@ -11669,7 +11672,7 @@
     </row>
     <row r="118" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="10" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B118" s="28" t="s">
         <v>103</v>
@@ -11679,17 +11682,17 @@
         <v>1</v>
       </c>
       <c r="D118" s="35" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E118" s="30"/>
       <c r="F118" s="10" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G118" s="28" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H118" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I118" s="14"/>
       <c r="J118" s="14"/>
@@ -11709,7 +11712,7 @@
     </row>
     <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="10" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B119" s="28" t="s">
         <v>33</v>
@@ -11719,17 +11722,17 @@
         <v>1</v>
       </c>
       <c r="D119" s="28" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E119" s="30"/>
       <c r="F119" s="30" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G119" s="28" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H119" s="28" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="I119" s="14"/>
       <c r="J119" s="14"/>
@@ -11738,7 +11741,7 @@
       <c r="M119" s="30"/>
       <c r="N119" s="30"/>
       <c r="O119" s="30" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P119" s="30"/>
       <c r="Q119" s="30"/>
@@ -11751,27 +11754,27 @@
     </row>
     <row r="120" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="10" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B120" s="28" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C120" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D120" s="28" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E120" s="30"/>
       <c r="F120" s="30" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G120" s="28" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H120" s="28" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="I120" s="14"/>
       <c r="J120" s="14"/>
@@ -11780,7 +11783,7 @@
       <c r="M120" s="30"/>
       <c r="N120" s="30"/>
       <c r="O120" s="46" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="P120" s="30"/>
       <c r="Q120" s="30"/>
@@ -11796,7 +11799,7 @@
     </row>
     <row r="121" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B121" s="28" t="s">
         <v>33</v>
@@ -11806,17 +11809,17 @@
         <v>1</v>
       </c>
       <c r="D121" s="28" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E121" s="30"/>
       <c r="F121" s="10" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G121" s="45" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H121" s="45" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="I121" s="14"/>
       <c r="J121" s="14"/>
@@ -11841,7 +11844,7 @@
     </row>
     <row r="122" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="10" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B122" s="28" t="s">
         <v>25</v>
@@ -11851,27 +11854,27 @@
         <v>1</v>
       </c>
       <c r="D122" s="28" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E122" s="30"/>
       <c r="F122" s="10" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G122" s="45" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H122" s="45" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="I122" s="14"/>
       <c r="J122" s="14"/>
       <c r="K122" s="14"/>
       <c r="L122" s="30"/>
       <c r="M122" s="30" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N122" s="8" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O122" s="30"/>
       <c r="P122" s="30"/>
@@ -11888,27 +11891,27 @@
     </row>
     <row r="123" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="10" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B123" s="28" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C123" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D123" s="28" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E123" s="30"/>
       <c r="F123" s="30" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G123" s="46" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H123" s="46" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="I123" s="14"/>
       <c r="J123" s="14"/>
@@ -11916,7 +11919,7 @@
       <c r="L123" s="30"/>
       <c r="M123" s="30"/>
       <c r="N123" s="30" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O123" s="30"/>
       <c r="P123" s="30"/>
@@ -11933,7 +11936,7 @@
     </row>
     <row r="124" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="35" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B124" s="33" t="s">
         <v>38</v>
@@ -11943,17 +11946,17 @@
         <v>1</v>
       </c>
       <c r="D124" s="28" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E124" s="30"/>
       <c r="F124" s="30" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G124" s="46" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H124" s="9" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="I124" s="14"/>
       <c r="J124" s="14"/>
@@ -11975,7 +11978,7 @@
     </row>
     <row r="125" customFormat="false" ht="46.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="10" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B125" s="28" t="s">
         <v>82</v>
@@ -11985,29 +11988,29 @@
         <v>1</v>
       </c>
       <c r="D125" s="28" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E125" s="30"/>
       <c r="F125" s="30" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G125" s="28" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H125" s="28" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I125" s="14"/>
       <c r="J125" s="14"/>
       <c r="K125" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L125" s="30"/>
       <c r="M125" s="30" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O125" s="30"/>
       <c r="P125" s="30"/>
@@ -12024,7 +12027,7 @@
     </row>
     <row r="126" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="10" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B126" s="28" t="s">
         <v>82</v>
@@ -12034,29 +12037,29 @@
         <v>1</v>
       </c>
       <c r="D126" s="28" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E126" s="30"/>
       <c r="F126" s="30" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G126" s="28" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H126" s="28" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I126" s="14"/>
       <c r="J126" s="14"/>
       <c r="K126" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L126" s="30"/>
       <c r="M126" s="30" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N126" s="10" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="O126" s="30"/>
       <c r="P126" s="30"/>
@@ -12073,27 +12076,27 @@
     </row>
     <row r="127" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="10" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B127" s="28" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C127" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D127" s="28" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E127" s="30"/>
       <c r="F127" s="30" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G127" s="46" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H127" s="46" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="I127" s="14"/>
       <c r="J127" s="14"/>
@@ -12101,12 +12104,12 @@
       <c r="L127" s="30"/>
       <c r="M127" s="30"/>
       <c r="N127" s="30" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O127" s="30"/>
       <c r="P127" s="30"/>
       <c r="Q127" s="46" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="R127" s="30"/>
       <c r="S127" s="28" t="b">
@@ -12120,7 +12123,7 @@
     </row>
     <row r="128" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="10" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B128" s="28" t="s">
         <v>109</v>
@@ -12130,17 +12133,17 @@
         <v>1</v>
       </c>
       <c r="D128" s="28" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E128" s="30"/>
       <c r="F128" s="30" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G128" s="46" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H128" s="46" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="I128" s="14"/>
       <c r="J128" s="14"/>
@@ -12148,7 +12151,7 @@
       <c r="L128" s="30"/>
       <c r="M128" s="30"/>
       <c r="N128" s="30" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O128" s="30"/>
       <c r="P128" s="30"/>
@@ -12165,27 +12168,27 @@
     </row>
     <row r="129" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="10" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B129" s="28" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C129" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D129" s="28" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E129" s="30"/>
       <c r="F129" s="30" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="G129" s="46" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H129" s="46" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I129" s="14"/>
       <c r="J129" s="14"/>
@@ -12193,12 +12196,12 @@
       <c r="L129" s="30"/>
       <c r="M129" s="30"/>
       <c r="N129" s="30" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O129" s="30"/>
       <c r="P129" s="30"/>
       <c r="Q129" s="46" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="R129" s="30"/>
       <c r="S129" s="28" t="b">
@@ -12212,27 +12215,27 @@
     </row>
     <row r="130" customFormat="false" ht="71.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="10" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B130" s="28" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C130" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D130" s="28" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E130" s="30"/>
       <c r="F130" s="30" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G130" s="46" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H130" s="46" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="I130" s="14"/>
       <c r="J130" s="14"/>
@@ -12240,12 +12243,12 @@
       <c r="L130" s="30"/>
       <c r="M130" s="30"/>
       <c r="N130" s="30" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O130" s="30"/>
       <c r="P130" s="30"/>
       <c r="Q130" s="46" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="R130" s="30"/>
       <c r="S130" s="28" t="n">
@@ -12259,27 +12262,27 @@
     </row>
     <row r="131" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="10" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B131" s="28" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C131" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D131" s="28" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E131" s="30"/>
       <c r="F131" s="30" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="G131" s="46" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H131" s="46" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="I131" s="14"/>
       <c r="J131" s="14"/>
@@ -12287,12 +12290,12 @@
       <c r="L131" s="30"/>
       <c r="M131" s="30"/>
       <c r="N131" s="30" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O131" s="30"/>
       <c r="P131" s="30"/>
       <c r="Q131" s="46" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="R131" s="30"/>
       <c r="S131" s="28" t="n">
@@ -12306,7 +12309,7 @@
     </row>
     <row r="132" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="10" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B132" s="28" t="s">
         <v>33</v>
@@ -12316,17 +12319,17 @@
         <v>1</v>
       </c>
       <c r="D132" s="28" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E132" s="30"/>
       <c r="F132" s="30" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G132" s="46" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H132" s="46" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="I132" s="14"/>
       <c r="J132" s="14"/>
@@ -12334,10 +12337,10 @@
       <c r="L132" s="30"/>
       <c r="M132" s="30"/>
       <c r="N132" s="30" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O132" s="30" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P132" s="30"/>
       <c r="Q132" s="30"/>
@@ -12353,7 +12356,7 @@
     </row>
     <row r="133" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="10" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B133" s="28" t="s">
         <v>103</v>
@@ -12363,17 +12366,17 @@
         <v>1</v>
       </c>
       <c r="D133" s="28" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E133" s="30"/>
       <c r="F133" s="10" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G133" s="28" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I133" s="14"/>
       <c r="J133" s="14"/>
@@ -12393,7 +12396,7 @@
     </row>
     <row r="134" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>38</v>
@@ -12403,16 +12406,16 @@
         <v>1</v>
       </c>
       <c r="D134" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="F134" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="F134" s="1" t="s">
-        <v>656</v>
-      </c>
       <c r="G134" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="L134" s="48"/>
       <c r="M134" s="49"/>
@@ -12506,34 +12509,34 @@
   <sheetData>
     <row r="1" s="54" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="52" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B1" s="52" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C1" s="52" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="53" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E1" s="52" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F1" s="52" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D2" s="55" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E2" s="10" t="n">
         <v>1</v>
@@ -12546,10 +12549,10 @@
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D3" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>2</v>
@@ -12558,114 +12561,114 @@
     </row>
     <row r="4" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10" t="s">
+        <v>670</v>
+      </c>
+      <c r="D4" s="55" t="s">
         <v>669</v>
       </c>
-      <c r="D4" s="55" t="s">
-        <v>667</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>670</v>
+      <c r="E4" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="F4" s="10"/>
     </row>
-    <row r="5" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="B5" s="10" t="s">
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10" t="s">
         <v>671</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>666</v>
-      </c>
       <c r="D5" s="55" t="s">
-        <v>667</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>1</v>
+        <v>668</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>672</v>
       </c>
       <c r="F5" s="10"/>
     </row>
-    <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>96</v>
+        <v>673</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D6" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" s="10"/>
     </row>
-    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="56" t="s">
-        <v>139</v>
-      </c>
-      <c r="B7" s="10"/>
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>673</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>675</v>
+      </c>
       <c r="C7" s="10" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D7" s="55" t="s">
-        <v>667</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>674</v>
+        <v>676</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="F7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>677</v>
-      </c>
       <c r="C9" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="D9" s="55" t="s">
         <v>676</v>
       </c>
-      <c r="D9" s="55" t="s">
-        <v>678</v>
-      </c>
       <c r="E9" s="10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>4</v>
@@ -12674,147 +12677,147 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C11" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="D11" s="55" t="s">
         <v>676</v>
       </c>
-      <c r="D11" s="55" t="s">
-        <v>678</v>
-      </c>
       <c r="E11" s="10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="D12" s="55" t="s">
         <v>676</v>
       </c>
-      <c r="D12" s="55" t="s">
-        <v>668</v>
-      </c>
       <c r="E12" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>680</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>677</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B13" s="10"/>
       <c r="C13" s="10" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D13" s="55" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>681</v>
+        <v>198</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D14" s="55" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="10"/>
+      <c r="I14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>133</v>
+        <v>680</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D15" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>197</v>
+        <v>149</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F16" s="10"/>
-      <c r="I16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>682</v>
+        <v>161</v>
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="D17" s="55" t="s">
         <v>676</v>
       </c>
-      <c r="D17" s="55" t="s">
-        <v>668</v>
-      </c>
       <c r="E17" s="10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="B18" s="10"/>
+        <v>161</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>675</v>
+      </c>
       <c r="C18" s="10" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D18" s="55" t="s">
-        <v>668</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>14</v>
+        <v>681</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>682</v>
       </c>
       <c r="F18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D19" s="55" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>15</v>
@@ -12823,475 +12826,443 @@
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>677</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="B20" s="10"/>
       <c r="C20" s="10" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D20" s="55" t="s">
-        <v>683</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>684</v>
+        <v>669</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>16</v>
       </c>
       <c r="F20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>179</v>
+        <v>683</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10" t="s">
+        <v>674</v>
+      </c>
+      <c r="D21" s="55" t="s">
         <v>676</v>
       </c>
-      <c r="D21" s="55" t="s">
-        <v>668</v>
-      </c>
       <c r="E21" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="B22" s="10"/>
+        <v>683</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>675</v>
+      </c>
       <c r="C22" s="10" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D22" s="55" t="s">
-        <v>668</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>16</v>
+        <v>681</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>682</v>
       </c>
       <c r="F22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D23" s="55" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="F23" s="10"/>
     </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10" t="s">
         <v>685</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>677</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>676</v>
-      </c>
       <c r="D24" s="55" t="s">
-        <v>683</v>
+        <v>668</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="F24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="s">
-        <v>686</v>
-      </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10" t="s">
-        <v>676</v>
+      <c r="A25" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="C25" s="50" t="s">
+        <v>687</v>
       </c>
       <c r="D25" s="55" t="s">
         <v>668</v>
       </c>
-      <c r="E25" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10" t="s">
+      <c r="E25" s="51" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="B26" s="50" t="s">
+        <v>689</v>
+      </c>
+      <c r="C26" s="50" t="s">
         <v>687</v>
       </c>
       <c r="D26" s="55" t="s">
-        <v>667</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>670</v>
-      </c>
-      <c r="F26" s="10"/>
+        <v>668</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="50" t="s">
-        <v>206</v>
+        <v>207</v>
+      </c>
+      <c r="B27" s="50" t="s">
+        <v>689</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D27" s="55" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="50" t="s">
-        <v>206</v>
-      </c>
-      <c r="B28" s="50" t="s">
-        <v>671</v>
+        <v>223</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D28" s="55" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E28" s="51" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="50" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="B29" s="50" t="s">
-        <v>671</v>
+        <v>689</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D29" s="55" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="50" t="s">
-        <v>222</v>
+        <v>223</v>
+      </c>
+      <c r="B30" s="50" t="s">
+        <v>689</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D30" s="55" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E30" s="51" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="50" t="s">
-        <v>222</v>
-      </c>
-      <c r="B31" s="50" t="s">
-        <v>671</v>
+        <v>232</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="D31" s="55" t="s">
-        <v>667</v>
-      </c>
-      <c r="E31" s="51" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>668</v>
+      </c>
+      <c r="E31" s="50" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="50" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B32" s="50" t="s">
-        <v>671</v>
+        <v>689</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="D32" s="55" t="s">
-        <v>667</v>
-      </c>
-      <c r="E32" s="51" t="s">
-        <v>691</v>
+        <v>668</v>
+      </c>
+      <c r="E32" s="50" t="s">
+        <v>696</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="50" t="s">
-        <v>231</v>
+        <v>232</v>
+      </c>
+      <c r="B33" s="50" t="s">
+        <v>689</v>
       </c>
       <c r="C33" s="50" t="s">
         <v>694</v>
       </c>
       <c r="D33" s="55" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E33" s="50" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="50" t="s">
+        <v>232</v>
+      </c>
+      <c r="B34" s="50" t="s">
+        <v>689</v>
+      </c>
+      <c r="C34" s="50" t="s">
+        <v>698</v>
+      </c>
+      <c r="D34" s="55" t="s">
+        <v>668</v>
+      </c>
+      <c r="E34" s="50" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="50" t="s">
-        <v>231</v>
-      </c>
-      <c r="B34" s="50" t="s">
-        <v>671</v>
-      </c>
-      <c r="C34" s="50" t="s">
-        <v>694</v>
-      </c>
-      <c r="D34" s="55" t="s">
-        <v>667</v>
-      </c>
-      <c r="E34" s="50" t="s">
+    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="50" t="s">
+        <v>232</v>
+      </c>
+      <c r="B35" s="50" t="s">
+        <v>689</v>
+      </c>
+      <c r="C35" s="50" t="s">
+        <v>698</v>
+      </c>
+      <c r="D35" s="55" t="s">
+        <v>668</v>
+      </c>
+      <c r="E35" s="50" t="s">
         <v>696</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="50" t="s">
-        <v>231</v>
-      </c>
-      <c r="B35" s="50" t="s">
-        <v>671</v>
-      </c>
-      <c r="C35" s="50" t="s">
-        <v>694</v>
-      </c>
-      <c r="D35" s="55" t="s">
-        <v>667</v>
-      </c>
-      <c r="E35" s="50" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B36" s="50" t="s">
-        <v>671</v>
+        <v>689</v>
       </c>
       <c r="C36" s="50" t="s">
         <v>698</v>
       </c>
       <c r="D36" s="55" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E36" s="50" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="50" t="s">
-        <v>231</v>
-      </c>
-      <c r="B37" s="50" t="s">
-        <v>671</v>
-      </c>
-      <c r="C37" s="50" t="s">
-        <v>698</v>
-      </c>
-      <c r="D37" s="55" t="s">
-        <v>667</v>
+        <v>41</v>
+      </c>
+      <c r="C37" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>668</v>
       </c>
       <c r="E37" s="50" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="50" t="s">
-        <v>231</v>
-      </c>
-      <c r="B38" s="50" t="s">
-        <v>671</v>
-      </c>
-      <c r="C38" s="50" t="s">
-        <v>698</v>
-      </c>
-      <c r="D38" s="55" t="s">
-        <v>667</v>
-      </c>
-      <c r="E38" s="50" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="58" t="s">
+        <v>602</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="D38" s="59" t="s">
+        <v>668</v>
+      </c>
+      <c r="E38" s="60" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="58" t="s">
+        <v>617</v>
+      </c>
+      <c r="C39" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="D39" s="55" t="s">
+        <v>669</v>
+      </c>
+      <c r="E39" s="50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="61" t="s">
+        <v>700</v>
+      </c>
+      <c r="C40" s="50" t="s">
+        <v>694</v>
+      </c>
+      <c r="D40" s="51" t="s">
+        <v>668</v>
+      </c>
+      <c r="E40" s="50" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="57" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="51" t="s">
-        <v>667</v>
-      </c>
-      <c r="E39" s="50" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="58" t="s">
-        <v>601</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="D40" s="59" t="s">
-        <v>667</v>
-      </c>
-      <c r="E40" s="60" t="s">
-        <v>670</v>
-      </c>
-    </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="58" t="s">
-        <v>616</v>
+      <c r="A41" s="20" t="s">
+        <v>267</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="D41" s="55" t="s">
         <v>668</v>
       </c>
-      <c r="E41" s="50" t="n">
-        <v>1</v>
+      <c r="E41" s="50" t="s">
+        <v>701</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="61" t="s">
-        <v>700</v>
+      <c r="A42" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="B42" s="50" t="s">
+        <v>689</v>
       </c>
       <c r="C42" s="50" t="s">
         <v>694</v>
       </c>
-      <c r="D42" s="51" t="s">
-        <v>667</v>
+      <c r="D42" s="55" t="s">
+        <v>668</v>
       </c>
       <c r="E42" s="50" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="20" t="s">
-        <v>266</v>
+        <v>696</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="56" t="s">
+        <v>175</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>694</v>
-      </c>
-      <c r="D43" s="55" t="s">
-        <v>667</v>
-      </c>
-      <c r="E43" s="50" t="s">
-        <v>701</v>
+        <v>687</v>
+      </c>
+      <c r="D43" s="51" t="s">
+        <v>668</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>702</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="B44" s="50" t="s">
-        <v>671</v>
+        <v>215</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="D44" s="55" t="s">
-        <v>667</v>
-      </c>
-      <c r="E44" s="50" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="56" t="s">
-        <v>174</v>
+        <v>668</v>
+      </c>
+      <c r="E44" s="51" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B45" s="50" t="s">
+        <v>689</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>688</v>
-      </c>
-      <c r="D45" s="51" t="s">
-        <v>667</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>702</v>
+        <v>703</v>
+      </c>
+      <c r="D45" s="55" t="s">
+        <v>668</v>
+      </c>
+      <c r="E45" s="51" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="C46" s="50" t="s">
-        <v>703</v>
-      </c>
-      <c r="D46" s="55" t="s">
-        <v>667</v>
-      </c>
-      <c r="E46" s="51" t="s">
-        <v>704</v>
+      <c r="A46" s="30" t="s">
+        <v>580</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="D46" s="59" t="s">
+        <v>668</v>
+      </c>
+      <c r="E46" s="60" t="s">
+        <v>686</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="B47" s="50" t="s">
-        <v>671</v>
-      </c>
-      <c r="C47" s="50" t="s">
-        <v>703</v>
-      </c>
-      <c r="D47" s="55" t="s">
-        <v>667</v>
-      </c>
-      <c r="E47" s="51" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="30" t="s">
-        <v>579</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>572</v>
-      </c>
-      <c r="D48" s="59" t="s">
-        <v>667</v>
-      </c>
-      <c r="E48" s="60" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>544</v>
-      </c>
-      <c r="D49" s="51" t="s">
-        <v>667</v>
-      </c>
-      <c r="E49" s="50" t="s">
-        <v>670</v>
-      </c>
-    </row>
+      <c r="A47" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="D47" s="51" t="s">
+        <v>668</v>
+      </c>
+      <c r="E47" s="50" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -13435,7 +13406,7 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>723</v>
@@ -13464,7 +13435,7 @@
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="35" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>726</v>
@@ -13493,7 +13464,7 @@
     </row>
     <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="35" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>728</v>
@@ -13519,7 +13490,7 @@
     </row>
     <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="35" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>729</v>
@@ -13545,7 +13516,7 @@
     </row>
     <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="35" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>732</v>
@@ -13574,7 +13545,7 @@
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>735</v>
@@ -13598,12 +13569,12 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>738</v>
@@ -13629,7 +13600,7 @@
     </row>
     <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>741</v>
@@ -13653,7 +13624,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
   </sheetData>
@@ -13688,7 +13659,7 @@
         <v>744</v>
       </c>
       <c r="B1" s="65" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C1" s="65" t="s">
         <v>6</v>
@@ -13714,10 +13685,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>670</v>
+        <v>686</v>
       </c>
       <c r="B2" s="67" t="s">
-        <v>670</v>
+        <v>686</v>
       </c>
       <c r="C2" s="67" t="s">
         <v>747</v>
@@ -13750,10 +13721,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="67" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B4" s="67" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C4" s="67" t="s">
         <v>752</v>
@@ -13771,7 +13742,7 @@
         <v>754</v>
       </c>
       <c r="B5" s="67" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C5" s="67" t="s">
         <v>755</v>
@@ -13804,10 +13775,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="67" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B7" s="67" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C7" s="67" t="s">
         <v>760</v>
@@ -13830,11 +13801,11 @@
       <c r="E8" s="67"/>
       <c r="F8" s="67"/>
       <c r="G8" s="67" t="s">
-        <v>670</v>
+        <v>686</v>
       </c>
       <c r="H8" s="67"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="67" t="s">
         <v>36</v>
       </c>
@@ -13847,10 +13818,11 @@
         <v>749</v>
       </c>
       <c r="H9" s="67"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I9" s="64"/>
+    </row>
+    <row r="10" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="67" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B10" s="67"/>
       <c r="C10" s="67"/>
@@ -13861,10 +13833,11 @@
         <v>36</v>
       </c>
       <c r="H10" s="67"/>
+      <c r="I10" s="64"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="67" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B11" s="67"/>
       <c r="C11" s="67"/>
@@ -13886,11 +13859,11 @@
       <c r="E12" s="67"/>
       <c r="F12" s="67"/>
       <c r="G12" s="67" t="s">
-        <v>670</v>
+        <v>686</v>
       </c>
       <c r="H12" s="67"/>
     </row>
-    <row r="13" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="67" t="s">
         <v>101</v>
       </c>
@@ -13903,9 +13876,8 @@
         <v>749</v>
       </c>
       <c r="H13" s="67"/>
-      <c r="I13" s="64"/>
-    </row>
-    <row r="14" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="67" t="s">
         <v>101</v>
       </c>
@@ -13915,14 +13887,13 @@
       <c r="E14" s="67"/>
       <c r="F14" s="67"/>
       <c r="G14" s="67" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="H14" s="67"/>
-      <c r="I14" s="64"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B15" s="67" t="s">
         <v>762</v>
@@ -13940,7 +13911,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B16" s="67" t="s">
         <v>765</v>
@@ -13958,7 +13929,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="68" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B17" s="67"/>
       <c r="C17" s="67"/>
@@ -13966,13 +13937,13 @@
       <c r="E17" s="67"/>
       <c r="F17" s="67"/>
       <c r="G17" s="67" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="H17" s="67"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="68" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B18" s="67" t="s">
         <v>762</v>
@@ -13990,7 +13961,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="68" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B19" s="67" t="s">
         <v>765</v>
@@ -14008,10 +13979,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="68" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B20" s="67" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="67" t="s">
         <v>770</v>
@@ -14026,7 +13997,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="68" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B21" s="67"/>
       <c r="C21" s="67"/>
@@ -14034,13 +14005,13 @@
       <c r="E21" s="67"/>
       <c r="F21" s="67"/>
       <c r="G21" s="67" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="H21" s="67"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="67" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B22" s="67" t="s">
         <v>704</v>
@@ -14058,7 +14029,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="67" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B23" s="67" t="s">
         <v>705</v>
@@ -14076,7 +14047,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="67" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B24" s="67"/>
       <c r="C24" s="67"/>
@@ -14090,7 +14061,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="67" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B25" s="67" t="s">
         <v>704</v>
@@ -14108,7 +14079,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="67" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B26" s="67" t="s">
         <v>705</v>
@@ -14126,7 +14097,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="67" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B27" s="67"/>
       <c r="C27" s="67"/>
@@ -14140,7 +14111,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="67" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B28" s="67" t="s">
         <v>780</v>
@@ -14155,12 +14126,12 @@
       <c r="F28" s="67"/>
       <c r="G28" s="67"/>
       <c r="H28" s="67" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="67" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B29" s="67" t="s">
         <v>783</v>
@@ -14175,12 +14146,12 @@
       <c r="F29" s="67"/>
       <c r="G29" s="67"/>
       <c r="H29" s="67" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="67" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B30" s="67" t="s">
         <v>786</v>
@@ -14195,12 +14166,12 @@
       <c r="F30" s="67"/>
       <c r="G30" s="67"/>
       <c r="H30" s="67" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="67" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B31" s="67" t="s">
         <v>789</v>
@@ -14215,12 +14186,12 @@
       <c r="F31" s="67"/>
       <c r="G31" s="67"/>
       <c r="H31" s="67" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="67" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B32" s="67" t="s">
         <v>792</v>
@@ -14235,12 +14206,12 @@
       <c r="F32" s="67"/>
       <c r="G32" s="67"/>
       <c r="H32" s="67" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="67" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B33" s="67" t="s">
         <v>795</v>
@@ -14255,12 +14226,12 @@
       <c r="F33" s="67"/>
       <c r="G33" s="67"/>
       <c r="H33" s="67" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="67" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B34" s="67"/>
       <c r="C34" s="67"/>
@@ -14268,16 +14239,16 @@
       <c r="E34" s="67"/>
       <c r="F34" s="67"/>
       <c r="G34" s="67" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H34" s="67"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="67" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B35" s="67" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C35" s="67" t="s">
         <v>798</v>
@@ -14295,7 +14266,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="67" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B36" s="67" t="s">
         <v>690</v>
@@ -14316,7 +14287,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="67" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B37" s="67" t="s">
         <v>691</v>
@@ -14337,7 +14308,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="67" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B38" s="67" t="s">
         <v>692</v>
@@ -14358,7 +14329,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="67" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B39" s="67" t="s">
         <v>693</v>
@@ -14379,7 +14350,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="67" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B40" s="67" t="s">
         <v>809</v>
@@ -14394,12 +14365,12 @@
       <c r="F40" s="67"/>
       <c r="G40" s="67"/>
       <c r="H40" s="67" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="67" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B41" s="67" t="s">
         <v>792</v>
@@ -14417,7 +14388,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="67" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B42" s="67" t="s">
         <v>812</v>
@@ -14435,7 +14406,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="67" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B43" s="69" t="s">
         <v>702</v>
@@ -14453,7 +14424,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="67" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="67" t="s">
         <v>817</v>
@@ -14471,7 +14442,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="67" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B45" s="67" t="s">
         <v>820</v>
@@ -14489,10 +14460,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="67" t="s">
+        <v>164</v>
+      </c>
+      <c r="B46" s="67" t="s">
         <v>163</v>
-      </c>
-      <c r="B46" s="67" t="s">
-        <v>162</v>
       </c>
       <c r="C46" s="67" t="s">
         <v>755</v>
@@ -14507,10 +14478,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="67" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B47" s="67" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C47" s="67" t="s">
         <v>823</v>
@@ -14525,7 +14496,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="67" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B48" s="67"/>
       <c r="C48" s="67"/>
@@ -14539,7 +14510,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="67" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B49" s="67" t="s">
         <v>825</v>
@@ -14557,7 +14528,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="67" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B50" s="67" t="s">
         <v>828</v>
@@ -14575,7 +14546,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="67" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B51" s="67"/>
       <c r="C51" s="67"/>
@@ -14589,7 +14560,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="68" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B52" s="67" t="s">
         <v>695</v>
@@ -14607,7 +14578,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="68" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B53" s="67" t="s">
         <v>696</v>
@@ -14625,7 +14596,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="68" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B54" s="67" t="s">
         <v>697</v>
@@ -14643,7 +14614,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="68" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B55" s="67" t="s">
         <v>837</v>
@@ -14661,7 +14632,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="68" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B56" s="67" t="s">
         <v>701</v>
@@ -14679,7 +14650,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="68" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B57" s="64" t="s">
         <v>695</v>
@@ -14693,7 +14664,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="68" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B58" s="64" t="s">
         <v>696</v>
@@ -14707,7 +14678,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="68" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B59" s="64" t="s">
         <v>701</v>
@@ -14719,9 +14690,9 @@
         <v>846</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="68" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B60" s="64" t="s">
         <v>847</v>
@@ -14732,10 +14703,15 @@
       <c r="D60" s="64" t="s">
         <v>849</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E60" s="64"/>
+      <c r="F60" s="64"/>
+      <c r="G60" s="64"/>
+      <c r="H60" s="64"/>
+      <c r="I60" s="64"/>
+    </row>
+    <row r="61" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="68" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B61" s="64" t="s">
         <v>850</v>
@@ -14746,10 +14722,15 @@
       <c r="D61" s="64" t="s">
         <v>852</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E61" s="64"/>
+      <c r="F61" s="64"/>
+      <c r="G61" s="64"/>
+      <c r="H61" s="64"/>
+      <c r="I61" s="64"/>
+    </row>
+    <row r="62" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="68" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B62" s="64" t="s">
         <v>853</v>
@@ -14760,10 +14741,15 @@
       <c r="D62" s="64" t="s">
         <v>855</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E62" s="64"/>
+      <c r="F62" s="64"/>
+      <c r="G62" s="64"/>
+      <c r="H62" s="64"/>
+      <c r="I62" s="64"/>
+    </row>
+    <row r="63" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="68" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B63" s="64" t="s">
         <v>856</v>
@@ -14774,10 +14760,15 @@
       <c r="D63" s="64" t="s">
         <v>858</v>
       </c>
+      <c r="E63" s="64"/>
+      <c r="F63" s="64"/>
+      <c r="G63" s="64"/>
+      <c r="H63" s="64"/>
+      <c r="I63" s="64"/>
     </row>
     <row r="64" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="67" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B64" s="67" t="s">
         <v>859</v>
@@ -14796,7 +14787,7 @@
     </row>
     <row r="65" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="67" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B65" s="67" t="s">
         <v>862</v>
@@ -14815,7 +14806,7 @@
     </row>
     <row r="66" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="67" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B66" s="67" t="s">
         <v>865</v>
@@ -14834,7 +14825,7 @@
     </row>
     <row r="67" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="67" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B67" s="67" t="s">
         <v>868</v>
@@ -14853,7 +14844,7 @@
     </row>
     <row r="68" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="67" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B68" s="67" t="s">
         <v>871</v>
@@ -14872,7 +14863,7 @@
     </row>
     <row r="69" s="2" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="67" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B69" s="67" t="s">
         <v>874</v>
@@ -14891,7 +14882,7 @@
     </row>
     <row r="70" s="2" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="67" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B70" s="67" t="s">
         <v>877</v>
@@ -14908,9 +14899,9 @@
       <c r="H70" s="67"/>
       <c r="I70" s="67"/>
     </row>
-    <row r="71" s="2" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="67" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B71" s="67" t="s">
         <v>880</v>
@@ -14927,9 +14918,9 @@
       <c r="H71" s="67"/>
       <c r="I71" s="67"/>
     </row>
-    <row r="72" s="2" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="67" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B72" s="67" t="s">
         <v>883</v>
@@ -14946,9 +14937,9 @@
       <c r="H72" s="67"/>
       <c r="I72" s="67"/>
     </row>
-    <row r="73" s="2" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="67" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B73" s="67" t="s">
         <v>757</v>
@@ -14965,9 +14956,9 @@
       <c r="H73" s="67"/>
       <c r="I73" s="67"/>
     </row>
-    <row r="74" s="2" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="67" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B74" s="67" t="s">
         <v>887</v>
@@ -14986,7 +14977,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="70" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B75" s="69" t="s">
         <v>888</v>
@@ -15000,7 +14991,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="70" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B76" s="64" t="s">
         <v>891</v>
@@ -15014,10 +15005,10 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="70" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B77" s="64" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C77" s="64" t="s">
         <v>755</v>
@@ -15028,10 +15019,10 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="70" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B78" s="64" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C78" s="69" t="s">
         <v>760</v>
@@ -15044,7 +15035,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="71" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B79" s="64" t="s">
         <v>895</v>
@@ -15056,12 +15047,12 @@
         <v>897</v>
       </c>
       <c r="H79" s="69" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="71" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B80" s="64" t="s">
         <v>898</v>
@@ -15075,12 +15066,12 @@
       <c r="E80" s="72"/>
       <c r="F80" s="72"/>
       <c r="H80" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="71" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B81" s="64" t="s">
         <v>901</v>
@@ -15094,7 +15085,7 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="71" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B82" s="64" t="s">
         <v>904</v>
@@ -15110,7 +15101,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="71" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B83" s="64" t="s">
         <v>907</v>
@@ -15126,7 +15117,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="71" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B84" s="64" t="s">
         <v>910</v>
@@ -15140,12 +15131,12 @@
       <c r="E84" s="69"/>
       <c r="F84" s="69"/>
       <c r="H84" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="71" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B85" s="64" t="s">
         <v>913</v>
@@ -15161,7 +15152,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="71" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B86" s="64" t="s">
         <v>916</v>
@@ -15175,15 +15166,15 @@
       <c r="E86" s="69"/>
       <c r="F86" s="69"/>
       <c r="H86" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="71" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B87" s="64" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C87" s="69" t="s">
         <v>755</v>
@@ -15228,7 +15219,7 @@
         <v>919</v>
       </c>
       <c r="B90" s="64" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C90" s="64" t="s">
         <v>923</v>
@@ -15316,7 +15307,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="71" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B95" s="69" t="s">
         <v>942</v>
@@ -15330,7 +15321,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="71" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B96" s="69" t="s">
         <v>945</v>
@@ -15344,7 +15335,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="71" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B97" s="69" t="s">
         <v>948</v>
@@ -15358,7 +15349,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="71" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B98" s="69" t="s">
         <v>951</v>
@@ -15372,7 +15363,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="71" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G99" s="67" t="s">
         <v>754</v>
@@ -15380,7 +15371,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="71" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G100" s="67" t="s">
         <v>757</v>
@@ -15388,7 +15379,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="71" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B101" s="69" t="s">
         <v>954</v>
@@ -15402,7 +15393,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="71" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B102" s="69" t="s">
         <v>957</v>
@@ -15416,7 +15407,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="71" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B103" s="69" t="s">
         <v>948</v>
@@ -15430,7 +15421,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="71" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B104" s="69" t="s">
         <v>960</v>
@@ -15444,7 +15435,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="71" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G105" s="67" t="s">
         <v>754</v>
@@ -15452,7 +15443,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="71" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G106" s="67" t="s">
         <v>757</v>
@@ -15460,7 +15451,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="73" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B107" s="69" t="s">
         <v>963</v>
@@ -15474,7 +15465,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="73" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B108" s="64" t="s">
         <v>966</v>
@@ -15488,7 +15479,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="73" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B109" s="69" t="s">
         <v>969</v>
@@ -15502,7 +15493,7 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="73" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B110" s="69" t="s">
         <v>972</v>
@@ -15516,7 +15507,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="73" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B111" s="69" t="s">
         <v>975</v>
@@ -15530,7 +15521,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="73" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B112" s="69" t="s">
         <v>978</v>
@@ -15544,10 +15535,10 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="73" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G113" s="67" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15729,7 +15720,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="46" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B2" s="46" t="s">
         <v>1014</v>
@@ -15767,7 +15758,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="46" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B3" s="46" t="s">
         <v>1022</v>
@@ -15805,7 +15796,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="46" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B4" s="46" t="s">
         <v>1029</v>
@@ -15843,7 +15834,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="46" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B5" s="46" t="s">
         <v>1022</v>
@@ -15959,7 +15950,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>1047</v>
@@ -15974,7 +15965,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>1050</v>
@@ -15988,7 +15979,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>1053</v>
@@ -16002,7 +15993,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>1056</v>
@@ -16016,7 +16007,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>1059</v>
@@ -16030,7 +16021,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>1062</v>
@@ -16044,7 +16035,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>1065</v>
@@ -16058,7 +16049,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>1068</v>
@@ -16072,7 +16063,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>1071</v>
@@ -16086,7 +16077,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>1074</v>
@@ -16100,7 +16091,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>1077</v>
@@ -16114,7 +16105,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>1078</v>
@@ -16128,7 +16119,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B16" s="35" t="s">
         <v>1081</v>
@@ -16148,7 +16139,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>1086</v>
@@ -16168,7 +16159,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>1091</v>
@@ -16188,7 +16179,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>1096</v>
@@ -16208,7 +16199,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>1101</v>
@@ -16228,7 +16219,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>1106</v>
@@ -16242,7 +16233,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>1109</v>
@@ -16256,7 +16247,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>1112</v>
@@ -16270,7 +16261,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>1115</v>
@@ -16284,7 +16275,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>1118</v>
@@ -16304,7 +16295,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>1123</v>
@@ -16318,7 +16309,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>1126</v>
@@ -16332,7 +16323,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>1129</v>
@@ -16346,7 +16337,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>1132</v>
@@ -16360,7 +16351,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>1135</v>
@@ -16374,7 +16365,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>1138</v>
@@ -16388,7 +16379,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>1141</v>
@@ -16402,7 +16393,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>1144</v>
@@ -16416,7 +16407,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>1147</v>
@@ -16430,7 +16421,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>1150</v>
@@ -16444,7 +16435,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>1153</v>
@@ -16458,7 +16449,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>1154</v>
@@ -16472,7 +16463,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>1157</v>
@@ -16486,7 +16477,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>1160</v>
@@ -16500,7 +16491,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>1163</v>
@@ -16514,7 +16505,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>1166</v>
@@ -16528,7 +16519,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>1169</v>
@@ -16542,7 +16533,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>1172</v>
@@ -16556,7 +16547,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>1175</v>
@@ -16570,7 +16561,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>1178</v>
@@ -16584,7 +16575,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>1181</v>
@@ -16598,7 +16589,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>1184</v>
@@ -16618,7 +16609,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>1189</v>
@@ -16638,7 +16629,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>1194</v>
@@ -16658,7 +16649,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>1199</v>
@@ -16678,7 +16669,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B51" s="46" t="s">
         <v>1204</v>
@@ -16698,7 +16689,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>1209</v>
@@ -16718,7 +16709,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>1214</v>
@@ -16904,7 +16895,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="30" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B65" s="61" t="s">
         <v>1254</v>
@@ -16920,7 +16911,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="30" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B66" s="61" t="s">
         <v>1255</v>
@@ -16936,7 +16927,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="30" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B67" s="61" t="s">
         <v>1256</v>
@@ -16952,7 +16943,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="30" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B68" s="10" t="s">
         <v>1257</v>
@@ -16972,7 +16963,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B69" s="61" t="s">
         <v>1258</v>
@@ -16992,7 +16983,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B70" s="61" t="s">
         <v>1259</v>
@@ -17012,7 +17003,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B71" s="61" t="s">
         <v>1260</v>
@@ -17028,7 +17019,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B72" s="61" t="s">
         <v>1263</v>
@@ -17044,7 +17035,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B73" s="61" t="s">
         <v>1266</v>
@@ -17060,7 +17051,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="30" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>1269</v>
@@ -17076,7 +17067,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B75" s="10" t="s">
         <v>1272</v>
@@ -17090,7 +17081,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B76" s="10" t="s">
         <v>1275</v>
@@ -17104,7 +17095,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B77" s="10" t="s">
         <v>1278</v>
@@ -17118,7 +17109,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>1281</v>
@@ -17232,7 +17223,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>1289</v>
@@ -17252,7 +17243,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>1294</v>
@@ -17272,7 +17263,7 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>1299</v>
@@ -17286,7 +17277,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>1302</v>
@@ -17300,7 +17291,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>1305</v>
@@ -17314,7 +17305,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>1308</v>
@@ -17328,7 +17319,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>1311</v>
@@ -17342,7 +17333,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>1314</v>
@@ -17356,7 +17347,7 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>1317</v>
@@ -17370,7 +17361,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>1320</v>
@@ -17384,7 +17375,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>1323</v>
@@ -17398,7 +17389,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>1325</v>
@@ -17412,7 +17403,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>1328</v>
@@ -17426,7 +17417,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>1331</v>
@@ -17440,7 +17431,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>1334</v>
@@ -17454,7 +17445,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>1337</v>
@@ -17468,7 +17459,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>1340</v>
@@ -17482,7 +17473,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>1343</v>
@@ -17496,7 +17487,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>1346</v>
@@ -17510,7 +17501,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>1349</v>
@@ -17524,7 +17515,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>1352</v>
@@ -17538,7 +17529,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>1355</v>
@@ -17552,7 +17543,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>1358</v>
@@ -17566,7 +17557,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>1361</v>
@@ -17580,7 +17571,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>1364</v>
@@ -17594,7 +17585,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>1367</v>
@@ -17608,7 +17599,7 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>1370</v>
@@ -17622,7 +17613,7 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>1373</v>
@@ -17636,7 +17627,7 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>1376</v>
@@ -17650,7 +17641,7 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>1379</v>
@@ -17664,7 +17655,7 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>1382</v>
@@ -17678,7 +17669,7 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>1385</v>
@@ -17694,7 +17685,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>1388</v>
@@ -17710,7 +17701,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>1391</v>
@@ -17726,7 +17717,7 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>1394</v>
@@ -17742,7 +17733,7 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>1397</v>
@@ -17758,7 +17749,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>1400</v>
@@ -17774,7 +17765,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>1403</v>
@@ -17790,7 +17781,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>1406</v>
@@ -17806,7 +17797,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>1408</v>
@@ -17822,7 +17813,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>1411</v>
@@ -17838,7 +17829,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>1414</v>
@@ -17854,7 +17845,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>1417</v>
@@ -17870,7 +17861,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>1420</v>
@@ -17886,7 +17877,7 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>1423</v>
@@ -17902,7 +17893,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>1426</v>
@@ -17918,7 +17909,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>1429</v>
@@ -17934,7 +17925,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>1432</v>
@@ -17950,7 +17941,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>1435</v>
@@ -17966,7 +17957,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>1438</v>
@@ -17982,7 +17973,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>1441</v>
@@ -17998,7 +17989,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>1444</v>
@@ -18014,7 +18005,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>1447</v>
@@ -18030,7 +18021,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>1450</v>
@@ -18046,7 +18037,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>1453</v>
@@ -18062,7 +18053,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>1456</v>
@@ -18078,7 +18069,7 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>1459</v>
@@ -18094,7 +18085,7 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>1462</v>
@@ -18110,7 +18101,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>1463</v>
@@ -18126,7 +18117,7 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>1466</v>

--- a/survey/references/OD_nationale_quebec_2025.xlsx
+++ b/survey/references/OD_nationale_quebec_2025.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Widgets" sheetId="1" state="visible" r:id="rId3"/>
@@ -1033,20 +1033,96 @@
     <t xml:space="preserve">personDidTrips</t>
   </si>
   <si>
-    <t xml:space="preserve">Est-ce que {{nickname}} s'est déplac{{gender:é/ée/é(e)/é(e)}} le {{assignedDate}}?
-__Inclure tous les déplacements, qu'ils soient pour des motifs personnels (achats, sorties, loisirs, etc.), pour le travail, ou pour aller chercher ou reconduire quelqu'un.__</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Did {{nickname}} make any trips on {{assignedDate}}?
-__Include all trips, whether for personal reasons (shopping, outings, leisure, etc.), for work, or to pick up or drop someone off.__</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vous êtes-vous déplac{{gender:é/ée/é(e)/é(e)}} le {{assignedDate}}?
-__Inclure tous les déplacements, qu'ils soient pour des motifs personnels (achats, sorties, loisirs, etc.), pour le travail, ou pour aller chercher ou reconduire quelqu'un.__</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Did you make any trips on {{assignedDate}}?
-__Include all trips, whether for personal reasons (shopping, outings, leisure, etc.), for work, or to pick up or drop someone off.__</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Est-ce que {{nickname}} s'est déplac{{gender:é/ée/é(e)/é(e)}} le {{assignedDate}}?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__Inclure tous les déplacements, peu importe la distance parcourue ou le mode de transport utilisé, qu'ils soient pour des motifs personnels (achats, sorties, loisirs, etc.), pour le travail, ou pour aller chercher ou reconduire quelqu'un.__</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Did {{nickname}} make any trips on {{assignedDate}}?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__Include all trips, regardless of the distance travelled or mode of transportation used, whether for personal reasons (shopping, outings, leisure, etc.), for work, or to pick up or drop someone off.__</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Vous êtes-vous déplac{{gender:é/ée/é(e)/é(e)}} le {{assignedDate}}?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__Inclure tous vos déplacements, peu importe la distance parcourue ou le mode de transport utilisé, qu'ils soient pour des motifs personnels (achats, sorties, loisirs, etc.), pour le travail, ou pour aller chercher ou reconduire quelqu'un.__</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Did you make any trips on {{assignedDate}}?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">__Include all trips, regardless of the distance travelled or mode of transportation used, whether for personal reasons (shopping, outings, leisure, etc.), for work, or to pick up or drop someone off.__</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">personDidTripsConfirm</t>
@@ -8691,7 +8767,7 @@
       <c r="V49" s="30"/>
       <c r="W49" s="30"/>
     </row>
-    <row r="50" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="140.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
         <v>295</v>
       </c>

--- a/survey/references/OD_nationale_quebec_2025.xlsx
+++ b/survey/references/OD_nationale_quebec_2025.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2450" uniqueCount="1469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2456" uniqueCount="1471">
   <si>
     <t xml:space="preserve">questionName</t>
   </si>
@@ -1690,7 +1690,10 @@
 overMaxAllowed</t>
   </si>
   <si>
-    <t xml:space="preserve">isSelfDeclaredCarDriverCustomConditional</t>
+    <t xml:space="preserve">isCarDriverCustomConditional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vehicleOccupancyExtraChoices</t>
   </si>
   <si>
     <t xml:space="preserve">segmentDriver</t>
@@ -3835,6 +3838,9 @@
   </si>
   <si>
     <t xml:space="preserve">No, I worked from home or from elsewhere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">isProxyCustomConditional</t>
   </si>
   <si>
     <t xml:space="preserve">inputRangeName</t>
@@ -10604,7 +10610,9 @@
         <v>466</v>
       </c>
       <c r="N92" s="30"/>
-      <c r="O92" s="30"/>
+      <c r="O92" s="30" t="s">
+        <v>467</v>
+      </c>
       <c r="P92" s="30"/>
       <c r="Q92" s="30"/>
       <c r="R92" s="30"/>
@@ -10619,7 +10627,7 @@
     </row>
     <row r="93" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B93" s="28" t="s">
         <v>280</v>
@@ -10635,13 +10643,13 @@
         <v>428</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G93" s="37" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I93" s="14"/>
       <c r="J93" s="14"/>
@@ -10664,7 +10672,7 @@
     </row>
     <row r="94" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B94" s="28" t="s">
         <v>72</v>
@@ -10680,13 +10688,13 @@
         <v>428</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H94" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I94" s="14"/>
       <c r="J94" s="14"/>
@@ -10707,12 +10715,12 @@
       <c r="V94" s="30"/>
       <c r="W94" s="30"/>
       <c r="X94" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="33.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B95" s="28" t="s">
         <v>72</v>
@@ -10728,13 +10736,13 @@
         <v>428</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I95" s="14"/>
       <c r="J95" s="14"/>
@@ -10755,12 +10763,12 @@
       <c r="V95" s="30"/>
       <c r="W95" s="30"/>
       <c r="X95" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B96" s="28" t="s">
         <v>33</v>
@@ -10776,24 +10784,24 @@
         <v>428</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H96" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I96" s="14"/>
       <c r="J96" s="14"/>
       <c r="K96" s="14"/>
       <c r="L96" s="30"/>
       <c r="M96" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N96" s="30"/>
       <c r="O96" s="30" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P96" s="30"/>
       <c r="Q96" s="30"/>
@@ -10809,7 +10817,7 @@
     </row>
     <row r="97" customFormat="false" ht="48.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B97" s="28" t="s">
         <v>25</v>
@@ -10825,23 +10833,23 @@
         <v>428</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I97" s="14"/>
       <c r="J97" s="14"/>
       <c r="K97" s="14"/>
       <c r="L97" s="30"/>
       <c r="M97" s="30" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N97" s="30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O97" s="30"/>
       <c r="P97" s="30"/>
@@ -10858,7 +10866,7 @@
     </row>
     <row r="98" customFormat="false" ht="39.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B98" s="28" t="s">
         <v>72</v>
@@ -10874,13 +10882,13 @@
         <v>428</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H98" s="10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I98" s="14"/>
       <c r="J98" s="14"/>
@@ -10898,12 +10906,12 @@
       <c r="V98" s="30"/>
       <c r="W98" s="30"/>
       <c r="X98" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B99" s="28" t="s">
         <v>280</v>
@@ -10939,7 +10947,7 @@
     </row>
     <row r="100" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="10" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B100" s="28" t="s">
         <v>280</v>
@@ -10955,13 +10963,13 @@
         <v>435</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="I100" s="14"/>
       <c r="J100" s="14"/>
@@ -10981,7 +10989,7 @@
     </row>
     <row r="101" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B101" s="28" t="s">
         <v>280</v>
@@ -10995,7 +11003,7 @@
       </c>
       <c r="E101" s="30"/>
       <c r="F101" s="30" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G101" s="10" t="s">
         <v>425</v>
@@ -11033,7 +11041,7 @@
         <v>1</v>
       </c>
       <c r="D102" s="28" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E102" s="30"/>
       <c r="F102" s="30"/>
@@ -11058,7 +11066,7 @@
       <c r="V102" s="30"/>
       <c r="W102" s="30"/>
       <c r="X102" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11073,7 +11081,7 @@
         <v>1</v>
       </c>
       <c r="D103" s="28" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E103" s="30"/>
       <c r="F103" s="30" t="s">
@@ -11101,12 +11109,12 @@
       <c r="V103" s="30"/>
       <c r="W103" s="30"/>
       <c r="X103" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="10" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B104" s="28" t="s">
         <v>72</v>
@@ -11116,17 +11124,17 @@
         <v>1</v>
       </c>
       <c r="D104" s="28" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E104" s="30"/>
       <c r="F104" s="30" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I104" s="14"/>
       <c r="J104" s="14"/>
@@ -11147,45 +11155,45 @@
       <c r="V104" s="30"/>
       <c r="W104" s="30"/>
       <c r="X104" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="10" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B105" s="28" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C105" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D105" s="28" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E105" s="30"/>
       <c r="F105" s="10" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="I105" s="14"/>
       <c r="J105" s="14"/>
       <c r="K105" s="14"/>
       <c r="L105" s="30"/>
       <c r="M105" s="30" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N105" s="30" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O105" s="30" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P105" s="30"/>
       <c r="Q105" s="30"/>
@@ -11198,7 +11206,7 @@
     </row>
     <row r="106" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="10" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B106" s="28" t="s">
         <v>72</v>
@@ -11208,31 +11216,31 @@
         <v>1</v>
       </c>
       <c r="D106" s="28" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E106" s="30"/>
       <c r="F106" s="10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H106" s="10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="J106" s="10" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K106" s="14"/>
       <c r="L106" s="30"/>
       <c r="M106" s="30" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N106" s="30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O106" s="30"/>
       <c r="P106" s="30"/>
@@ -11247,12 +11255,12 @@
       <c r="V106" s="30"/>
       <c r="W106" s="30"/>
       <c r="X106" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B107" s="28" t="s">
         <v>72</v>
@@ -11262,17 +11270,17 @@
         <v>1</v>
       </c>
       <c r="D107" s="28" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E107" s="30"/>
       <c r="F107" s="30" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I107" s="14"/>
       <c r="J107" s="14"/>
@@ -11293,45 +11301,45 @@
       <c r="V107" s="30"/>
       <c r="W107" s="30"/>
       <c r="X107" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B108" s="28" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C108" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D108" s="28" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E108" s="30"/>
       <c r="F108" s="10" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G108" s="10" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H108" s="10" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="I108" s="14"/>
       <c r="J108" s="14"/>
       <c r="K108" s="14"/>
       <c r="L108" s="30"/>
       <c r="M108" s="30" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N108" s="30" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O108" s="30" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P108" s="30"/>
       <c r="Q108" s="30"/>
@@ -11344,7 +11352,7 @@
     </row>
     <row r="109" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="10" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B109" s="28" t="s">
         <v>72</v>
@@ -11354,31 +11362,31 @@
         <v>1</v>
       </c>
       <c r="D109" s="28" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E109" s="30"/>
       <c r="F109" s="10" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="J109" s="10" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="K109" s="2"/>
       <c r="L109" s="30"/>
       <c r="M109" s="30" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N109" s="30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O109" s="30"/>
       <c r="P109" s="30"/>
@@ -11393,12 +11401,12 @@
       <c r="V109" s="30"/>
       <c r="W109" s="30"/>
       <c r="X109" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="36.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B110" s="28" t="s">
         <v>103</v>
@@ -11408,11 +11416,11 @@
         <v>1</v>
       </c>
       <c r="D110" s="28" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E110" s="30"/>
       <c r="F110" s="30" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="G110" s="28" t="s">
         <v>327</v>
@@ -11438,7 +11446,7 @@
     </row>
     <row r="111" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B111" s="28" t="s">
         <v>33</v>
@@ -11448,23 +11456,23 @@
         <v>1</v>
       </c>
       <c r="D111" s="35" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E111" s="30"/>
       <c r="F111" s="10" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="G111" s="38" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H111" s="38" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="I111" s="39" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="J111" s="38" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K111" s="30"/>
       <c r="L111" s="30"/>
@@ -11487,7 +11495,7 @@
     </row>
     <row r="112" s="2" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="40" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B112" s="40" t="s">
         <v>72</v>
@@ -11497,7 +11505,7 @@
         <v>1</v>
       </c>
       <c r="D112" s="35" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E112" s="41"/>
       <c r="F112" s="40" t="str">
@@ -11517,12 +11525,12 @@
         <v>1</v>
       </c>
       <c r="X112" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="113" s="2" customFormat="true" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="40" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B113" s="28" t="s">
         <v>33</v>
@@ -11532,32 +11540,32 @@
         <v>1</v>
       </c>
       <c r="D113" s="35" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E113" s="41"/>
       <c r="F113" s="40" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G113" s="42" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H113" s="44" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I113" s="42" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="J113" s="44" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K113" s="1"/>
       <c r="L113" s="1"/>
       <c r="M113" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N113" s="1"/>
       <c r="O113" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="S113" s="14" t="b">
         <f aca="false">TRUE()</f>
@@ -11566,7 +11574,7 @@
     </row>
     <row r="114" s="2" customFormat="true" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="40" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B114" s="28" t="s">
         <v>33</v>
@@ -11576,32 +11584,32 @@
         <v>1</v>
       </c>
       <c r="D114" s="35" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E114" s="41"/>
       <c r="F114" s="40" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G114" s="42" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H114" s="44" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I114" s="42" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="J114" s="44" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K114" s="1"/>
       <c r="L114" s="1"/>
       <c r="M114" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N114" s="1"/>
       <c r="O114" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="S114" s="14" t="b">
         <f aca="false">TRUE()</f>
@@ -11610,7 +11618,7 @@
     </row>
     <row r="115" s="2" customFormat="true" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="40" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B115" s="28" t="s">
         <v>33</v>
@@ -11620,32 +11628,32 @@
         <v>1</v>
       </c>
       <c r="D115" s="35" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E115" s="41"/>
       <c r="F115" s="40" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="G115" s="42" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H115" s="44" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="I115" s="42" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="J115" s="44" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="K115" s="1"/>
       <c r="L115" s="1"/>
       <c r="M115" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N115" s="1"/>
       <c r="O115" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="S115" s="14" t="b">
         <f aca="false">TRUE()</f>
@@ -11654,7 +11662,7 @@
     </row>
     <row r="116" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="10" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B116" s="28" t="s">
         <v>33</v>
@@ -11664,24 +11672,24 @@
         <v>1</v>
       </c>
       <c r="D116" s="35" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E116" s="30"/>
       <c r="F116" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G116" s="45" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H116" s="45" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="I116" s="14"/>
       <c r="J116" s="14"/>
       <c r="K116" s="14"/>
       <c r="L116" s="30"/>
       <c r="M116" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="30" t="s">
@@ -11701,7 +11709,7 @@
     </row>
     <row r="117" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="10" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B117" s="28" t="s">
         <v>25</v>
@@ -11711,27 +11719,27 @@
         <v>1</v>
       </c>
       <c r="D117" s="35" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E117" s="30"/>
       <c r="F117" s="10" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="G117" s="45" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H117" s="45" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="I117" s="14"/>
       <c r="J117" s="14"/>
       <c r="K117" s="14"/>
       <c r="L117" s="30"/>
       <c r="M117" s="30" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N117" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O117" s="30"/>
       <c r="P117" s="30"/>
@@ -11748,7 +11756,7 @@
     </row>
     <row r="118" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="10" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B118" s="28" t="s">
         <v>103</v>
@@ -11758,11 +11766,11 @@
         <v>1</v>
       </c>
       <c r="D118" s="35" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E118" s="30"/>
       <c r="F118" s="10" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G118" s="28" t="s">
         <v>327</v>
@@ -11788,7 +11796,7 @@
     </row>
     <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="10" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B119" s="28" t="s">
         <v>33</v>
@@ -11798,17 +11806,17 @@
         <v>1</v>
       </c>
       <c r="D119" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E119" s="30"/>
       <c r="F119" s="30" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G119" s="28" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H119" s="28" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="I119" s="14"/>
       <c r="J119" s="14"/>
@@ -11817,7 +11825,7 @@
       <c r="M119" s="30"/>
       <c r="N119" s="30"/>
       <c r="O119" s="30" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P119" s="30"/>
       <c r="Q119" s="30"/>
@@ -11830,27 +11838,27 @@
     </row>
     <row r="120" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="10" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B120" s="28" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C120" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D120" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E120" s="30"/>
       <c r="F120" s="30" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G120" s="28" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H120" s="28" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="I120" s="14"/>
       <c r="J120" s="14"/>
@@ -11859,7 +11867,7 @@
       <c r="M120" s="30"/>
       <c r="N120" s="30"/>
       <c r="O120" s="46" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P120" s="30"/>
       <c r="Q120" s="30"/>
@@ -11875,7 +11883,7 @@
     </row>
     <row r="121" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="10" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B121" s="28" t="s">
         <v>33</v>
@@ -11885,17 +11893,17 @@
         <v>1</v>
       </c>
       <c r="D121" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E121" s="30"/>
       <c r="F121" s="10" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G121" s="45" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H121" s="45" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="I121" s="14"/>
       <c r="J121" s="14"/>
@@ -11920,7 +11928,7 @@
     </row>
     <row r="122" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="10" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B122" s="28" t="s">
         <v>25</v>
@@ -11930,27 +11938,27 @@
         <v>1</v>
       </c>
       <c r="D122" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E122" s="30"/>
       <c r="F122" s="10" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G122" s="45" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H122" s="45" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="I122" s="14"/>
       <c r="J122" s="14"/>
       <c r="K122" s="14"/>
       <c r="L122" s="30"/>
       <c r="M122" s="30" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N122" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O122" s="30"/>
       <c r="P122" s="30"/>
@@ -11967,27 +11975,27 @@
     </row>
     <row r="123" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="10" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B123" s="28" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C123" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D123" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E123" s="30"/>
       <c r="F123" s="30" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="G123" s="46" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H123" s="46" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I123" s="14"/>
       <c r="J123" s="14"/>
@@ -11995,7 +12003,7 @@
       <c r="L123" s="30"/>
       <c r="M123" s="30"/>
       <c r="N123" s="30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O123" s="30"/>
       <c r="P123" s="30"/>
@@ -12012,7 +12020,7 @@
     </row>
     <row r="124" customFormat="false" ht="76.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="35" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B124" s="33" t="s">
         <v>38</v>
@@ -12022,17 +12030,17 @@
         <v>1</v>
       </c>
       <c r="D124" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E124" s="30"/>
       <c r="F124" s="30" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G124" s="46" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H124" s="9" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I124" s="14"/>
       <c r="J124" s="14"/>
@@ -12054,7 +12062,7 @@
     </row>
     <row r="125" customFormat="false" ht="46.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="10" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B125" s="28" t="s">
         <v>82</v>
@@ -12064,29 +12072,29 @@
         <v>1</v>
       </c>
       <c r="D125" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E125" s="30"/>
       <c r="F125" s="30" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G125" s="28" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H125" s="28" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I125" s="14"/>
       <c r="J125" s="14"/>
       <c r="K125" s="8" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L125" s="30"/>
       <c r="M125" s="30" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O125" s="30"/>
       <c r="P125" s="30"/>
@@ -12103,7 +12111,7 @@
     </row>
     <row r="126" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="10" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B126" s="28" t="s">
         <v>82</v>
@@ -12113,29 +12121,29 @@
         <v>1</v>
       </c>
       <c r="D126" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E126" s="30"/>
       <c r="F126" s="30" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G126" s="28" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H126" s="28" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="I126" s="14"/>
       <c r="J126" s="14"/>
       <c r="K126" s="8" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L126" s="30"/>
       <c r="M126" s="30" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N126" s="10" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O126" s="30"/>
       <c r="P126" s="30"/>
@@ -12152,27 +12160,27 @@
     </row>
     <row r="127" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="10" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B127" s="28" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C127" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D127" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E127" s="30"/>
       <c r="F127" s="30" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G127" s="46" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H127" s="46" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="I127" s="14"/>
       <c r="J127" s="14"/>
@@ -12180,12 +12188,12 @@
       <c r="L127" s="30"/>
       <c r="M127" s="30"/>
       <c r="N127" s="30" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O127" s="30"/>
       <c r="P127" s="30"/>
       <c r="Q127" s="46" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="R127" s="30"/>
       <c r="S127" s="28" t="b">
@@ -12199,7 +12207,7 @@
     </row>
     <row r="128" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="10" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B128" s="28" t="s">
         <v>109</v>
@@ -12209,17 +12217,17 @@
         <v>1</v>
       </c>
       <c r="D128" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E128" s="30"/>
       <c r="F128" s="30" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G128" s="46" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H128" s="46" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="I128" s="14"/>
       <c r="J128" s="14"/>
@@ -12227,7 +12235,7 @@
       <c r="L128" s="30"/>
       <c r="M128" s="30"/>
       <c r="N128" s="30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O128" s="30"/>
       <c r="P128" s="30"/>
@@ -12244,27 +12252,27 @@
     </row>
     <row r="129" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="10" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B129" s="28" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C129" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D129" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E129" s="30"/>
       <c r="F129" s="30" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G129" s="46" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H129" s="46" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="I129" s="14"/>
       <c r="J129" s="14"/>
@@ -12272,12 +12280,12 @@
       <c r="L129" s="30"/>
       <c r="M129" s="30"/>
       <c r="N129" s="30" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O129" s="30"/>
       <c r="P129" s="30"/>
       <c r="Q129" s="46" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="R129" s="30"/>
       <c r="S129" s="28" t="b">
@@ -12291,27 +12299,27 @@
     </row>
     <row r="130" customFormat="false" ht="71.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="10" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B130" s="28" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C130" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D130" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E130" s="30"/>
       <c r="F130" s="30" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G130" s="46" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H130" s="46" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="I130" s="14"/>
       <c r="J130" s="14"/>
@@ -12319,12 +12327,12 @@
       <c r="L130" s="30"/>
       <c r="M130" s="30"/>
       <c r="N130" s="30" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O130" s="30"/>
       <c r="P130" s="30"/>
       <c r="Q130" s="46" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="R130" s="30"/>
       <c r="S130" s="28" t="n">
@@ -12338,27 +12346,27 @@
     </row>
     <row r="131" customFormat="false" ht="61.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="10" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B131" s="28" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C131" s="29" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D131" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E131" s="30"/>
       <c r="F131" s="30" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G131" s="46" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H131" s="46" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="I131" s="14"/>
       <c r="J131" s="14"/>
@@ -12366,12 +12374,12 @@
       <c r="L131" s="30"/>
       <c r="M131" s="30"/>
       <c r="N131" s="30" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O131" s="30"/>
       <c r="P131" s="30"/>
       <c r="Q131" s="46" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="R131" s="30"/>
       <c r="S131" s="28" t="n">
@@ -12385,7 +12393,7 @@
     </row>
     <row r="132" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="10" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B132" s="28" t="s">
         <v>33</v>
@@ -12395,17 +12403,17 @@
         <v>1</v>
       </c>
       <c r="D132" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E132" s="30"/>
       <c r="F132" s="30" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="G132" s="46" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H132" s="46" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="I132" s="14"/>
       <c r="J132" s="14"/>
@@ -12413,7 +12421,7 @@
       <c r="L132" s="30"/>
       <c r="M132" s="30"/>
       <c r="N132" s="30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O132" s="30" t="s">
         <v>185</v>
@@ -12432,7 +12440,7 @@
     </row>
     <row r="133" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="10" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B133" s="28" t="s">
         <v>103</v>
@@ -12442,17 +12450,17 @@
         <v>1</v>
       </c>
       <c r="D133" s="28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E133" s="30"/>
       <c r="F133" s="10" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G133" s="28" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="I133" s="14"/>
       <c r="J133" s="14"/>
@@ -12472,7 +12480,7 @@
     </row>
     <row r="134" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>38</v>
@@ -12482,16 +12490,16 @@
         <v>1</v>
       </c>
       <c r="D134" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="F134" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="F134" s="1" t="s">
-        <v>657</v>
-      </c>
       <c r="G134" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L134" s="48"/>
       <c r="M134" s="49"/>
@@ -12585,34 +12593,34 @@
   <sheetData>
     <row r="1" s="54" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="52" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B1" s="52" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C1" s="52" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="53" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E1" s="52" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F1" s="52" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D2" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E2" s="10" t="n">
         <v>1</v>
@@ -12625,10 +12633,10 @@
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D3" s="55" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>2</v>
@@ -12641,10 +12649,10 @@
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="D4" s="55" t="s">
         <v>670</v>
-      </c>
-      <c r="D4" s="55" t="s">
-        <v>669</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>1</v>
@@ -12657,26 +12665,26 @@
       </c>
       <c r="B5" s="10"/>
       <c r="C5" s="10" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D5" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B6" s="10"/>
       <c r="C6" s="10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D6" s="55" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E6" s="10" t="n">
         <v>3</v>
@@ -12685,16 +12693,16 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>674</v>
-      </c>
       <c r="D7" s="55" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E7" s="10" t="n">
         <v>5</v>
@@ -12703,14 +12711,14 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D8" s="55" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>4</v>
@@ -12719,16 +12727,16 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
+        <v>678</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="D9" s="55" t="s">
         <v>677</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>675</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>674</v>
-      </c>
-      <c r="D9" s="55" t="s">
-        <v>676</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>13</v>
@@ -12737,14 +12745,14 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D10" s="55" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E10" s="10" t="n">
         <v>4</v>
@@ -12753,16 +12761,16 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>674</v>
-      </c>
       <c r="D11" s="55" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>15</v>
@@ -12771,14 +12779,14 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D12" s="55" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>5</v>
@@ -12791,10 +12799,10 @@
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D13" s="55" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>5</v>
@@ -12807,10 +12815,10 @@
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D14" s="55" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E14" s="10" t="n">
         <v>6</v>
@@ -12820,14 +12828,14 @@
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D15" s="55" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E15" s="10" t="n">
         <v>11</v>
@@ -12840,10 +12848,10 @@
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D16" s="55" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>14</v>
@@ -12856,10 +12864,10 @@
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D17" s="55" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E17" s="10" t="n">
         <v>15</v>
@@ -12871,16 +12879,16 @@
         <v>161</v>
       </c>
       <c r="B18" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>674</v>
-      </c>
       <c r="D18" s="55" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F18" s="10"/>
     </row>
@@ -12890,10 +12898,10 @@
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D19" s="55" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>15</v>
@@ -12906,10 +12914,10 @@
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D20" s="55" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>16</v>
@@ -12918,14 +12926,14 @@
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D21" s="55" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>16</v>
@@ -12934,32 +12942,32 @@
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
+        <v>684</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="D22" s="55" t="s">
+        <v>682</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>683</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>675</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>674</v>
-      </c>
-      <c r="D22" s="55" t="s">
-        <v>681</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>682</v>
       </c>
       <c r="F22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D23" s="55" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>40</v>
@@ -12972,13 +12980,13 @@
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="10" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D24" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F24" s="10"/>
     </row>
@@ -12987,13 +12995,13 @@
         <v>207</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D25" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13001,16 +13009,16 @@
         <v>207</v>
       </c>
       <c r="B26" s="50" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D26" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E26" s="51" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13018,16 +13026,16 @@
         <v>207</v>
       </c>
       <c r="B27" s="50" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D27" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13035,13 +13043,13 @@
         <v>223</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D28" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E28" s="51" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13049,16 +13057,16 @@
         <v>223</v>
       </c>
       <c r="B29" s="50" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D29" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13066,16 +13074,16 @@
         <v>223</v>
       </c>
       <c r="B30" s="50" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D30" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E30" s="51" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13083,13 +13091,13 @@
         <v>232</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D31" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E31" s="50" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13097,16 +13105,16 @@
         <v>232</v>
       </c>
       <c r="B32" s="50" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C32" s="50" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D32" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E32" s="50" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13114,16 +13122,16 @@
         <v>232</v>
       </c>
       <c r="B33" s="50" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C33" s="50" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D33" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E33" s="50" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13131,16 +13139,16 @@
         <v>232</v>
       </c>
       <c r="B34" s="50" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C34" s="50" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D34" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E34" s="50" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13148,16 +13156,16 @@
         <v>232</v>
       </c>
       <c r="B35" s="50" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C35" s="50" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D35" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E35" s="50" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13165,16 +13173,16 @@
         <v>232</v>
       </c>
       <c r="B36" s="50" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C36" s="50" t="s">
+        <v>699</v>
+      </c>
+      <c r="D36" s="55" t="s">
+        <v>669</v>
+      </c>
+      <c r="E36" s="50" t="s">
         <v>698</v>
-      </c>
-      <c r="D36" s="55" t="s">
-        <v>668</v>
-      </c>
-      <c r="E36" s="50" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13185,35 +13193,35 @@
         <v>32</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E37" s="50" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="58" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D38" s="59" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E38" s="60" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="58" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D39" s="55" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E39" s="50" t="n">
         <v>1</v>
@@ -13221,16 +13229,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="61" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D40" s="51" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E40" s="50" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13238,13 +13246,13 @@
         <v>267</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D41" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E41" s="50" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13252,16 +13260,16 @@
         <v>267</v>
       </c>
       <c r="B42" s="50" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D42" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E42" s="50" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13269,13 +13277,13 @@
         <v>175</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D43" s="51" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13283,13 +13291,13 @@
         <v>215</v>
       </c>
       <c r="C44" s="50" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D44" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E44" s="51" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13297,44 +13305,44 @@
         <v>215</v>
       </c>
       <c r="B45" s="50" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="D45" s="55" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="30" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D46" s="59" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E46" s="60" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D47" s="51" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -13381,25 +13389,25 @@
         <v>3</v>
       </c>
       <c r="B1" s="63" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C1" s="62" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D1" s="62" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E1" s="62" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F1" s="62" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1" s="62" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13407,13 +13415,13 @@
         <v>26</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E2" s="50" t="b">
         <f aca="false">TRUE()</f>
@@ -13433,13 +13441,13 @@
         <v>107</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E3" s="50" t="b">
         <f aca="false">TRUE()</f>
@@ -13456,16 +13464,16 @@
     </row>
     <row r="4" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E4" s="50" t="b">
         <f aca="false">TRUE()</f>
@@ -13485,13 +13493,13 @@
         <v>272</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E5" s="50" t="b">
         <f aca="false">FALSE()</f>
@@ -13506,7 +13514,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13514,13 +13522,13 @@
         <v>281</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E6" s="50" t="b">
         <f aca="false">FALSE()</f>
@@ -13535,7 +13543,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13543,13 +13551,13 @@
         <v>332</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E7" s="50" t="b">
         <f aca="false">FALSE()</f>
@@ -13561,7 +13569,7 @@
       </c>
       <c r="G7" s="50"/>
       <c r="H7" s="10" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13569,13 +13577,13 @@
         <v>428</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E8" s="50" t="b">
         <f aca="false">FALSE()</f>
@@ -13587,21 +13595,21 @@
       </c>
       <c r="G8" s="50"/>
       <c r="H8" s="10" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="35" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E9" s="50" t="b">
         <f aca="false">FALSE()</f>
@@ -13616,21 +13624,21 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="35" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E10" s="50" t="b">
         <f aca="false">FALSE()</f>
@@ -13645,21 +13653,21 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E11" s="50" t="b">
         <f aca="false">TRUE()</f>
@@ -13676,16 +13684,16 @@
     </row>
     <row r="12" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E12" s="50" t="b">
         <f aca="false">FALSE()</f>
@@ -13700,7 +13708,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -13732,10 +13740,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="65" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B1" s="65" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C1" s="65" t="s">
         <v>6</v>
@@ -13750,27 +13758,27 @@
         <v>9</v>
       </c>
       <c r="G1" s="65" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1" s="65" t="s">
         <v>12</v>
       </c>
       <c r="I1" s="64" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="67" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B2" s="67" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C2" s="67" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D2" s="67" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="E2" s="67"/>
       <c r="F2" s="67"/>
@@ -13779,16 +13787,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="67" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B3" s="67" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C3" s="67" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D3" s="67" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E3" s="67"/>
       <c r="F3" s="67"/>
@@ -13803,10 +13811,10 @@
         <v>163</v>
       </c>
       <c r="C4" s="67" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D4" s="67" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E4" s="67"/>
       <c r="F4" s="67"/>
@@ -13815,16 +13823,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="67" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B5" s="67" t="s">
         <v>163</v>
       </c>
       <c r="C5" s="67" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D5" s="67" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E5" s="67"/>
       <c r="F5" s="67"/>
@@ -13833,16 +13841,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="67" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B6" s="67" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C6" s="67" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D6" s="67" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E6" s="67"/>
       <c r="F6" s="67"/>
@@ -13851,16 +13859,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="67" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B7" s="67" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C7" s="67" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D7" s="67" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E7" s="67"/>
       <c r="F7" s="67"/>
@@ -13877,7 +13885,7 @@
       <c r="E8" s="67"/>
       <c r="F8" s="67"/>
       <c r="G8" s="67" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H8" s="67"/>
     </row>
@@ -13891,7 +13899,7 @@
       <c r="E9" s="67"/>
       <c r="F9" s="67"/>
       <c r="G9" s="67" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H9" s="67"/>
       <c r="I9" s="64"/>
@@ -13921,7 +13929,7 @@
       <c r="E11" s="67"/>
       <c r="F11" s="67"/>
       <c r="G11" s="67" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H11" s="67"/>
     </row>
@@ -13935,7 +13943,7 @@
       <c r="E12" s="67"/>
       <c r="F12" s="67"/>
       <c r="G12" s="67" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H12" s="67"/>
     </row>
@@ -13949,7 +13957,7 @@
       <c r="E13" s="67"/>
       <c r="F13" s="67"/>
       <c r="G13" s="67" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H13" s="67"/>
     </row>
@@ -13963,7 +13971,7 @@
       <c r="E14" s="67"/>
       <c r="F14" s="67"/>
       <c r="G14" s="67" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H14" s="67"/>
     </row>
@@ -13972,13 +13980,13 @@
         <v>135</v>
       </c>
       <c r="B15" s="67" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C15" s="67" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D15" s="67" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E15" s="67"/>
       <c r="F15" s="67"/>
@@ -13990,13 +13998,13 @@
         <v>135</v>
       </c>
       <c r="B16" s="67" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C16" s="67" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D16" s="67" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E16" s="67"/>
       <c r="F16" s="67"/>
@@ -14013,7 +14021,7 @@
       <c r="E17" s="67"/>
       <c r="F17" s="67"/>
       <c r="G17" s="67" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H17" s="67"/>
     </row>
@@ -14022,13 +14030,13 @@
         <v>141</v>
       </c>
       <c r="B18" s="67" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C18" s="67" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D18" s="67" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E18" s="67"/>
       <c r="F18" s="67"/>
@@ -14040,13 +14048,13 @@
         <v>141</v>
       </c>
       <c r="B19" s="67" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C19" s="67" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D19" s="67" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="E19" s="67"/>
       <c r="F19" s="67"/>
@@ -14061,10 +14069,10 @@
         <v>143</v>
       </c>
       <c r="C20" s="67" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D20" s="67" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E20" s="67"/>
       <c r="F20" s="67"/>
@@ -14081,7 +14089,7 @@
       <c r="E21" s="67"/>
       <c r="F21" s="67"/>
       <c r="G21" s="67" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H21" s="67"/>
     </row>
@@ -14090,13 +14098,13 @@
         <v>150</v>
       </c>
       <c r="B22" s="67" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C22" s="67" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D22" s="67" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E22" s="67"/>
       <c r="F22" s="67"/>
@@ -14108,13 +14116,13 @@
         <v>150</v>
       </c>
       <c r="B23" s="67" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C23" s="67" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D23" s="67" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E23" s="67"/>
       <c r="F23" s="67"/>
@@ -14131,7 +14139,7 @@
       <c r="E24" s="67"/>
       <c r="F24" s="67"/>
       <c r="G24" s="67" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H24" s="67"/>
     </row>
@@ -14140,13 +14148,13 @@
         <v>156</v>
       </c>
       <c r="B25" s="67" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C25" s="67" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D25" s="67" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E25" s="67"/>
       <c r="F25" s="67"/>
@@ -14158,13 +14166,13 @@
         <v>156</v>
       </c>
       <c r="B26" s="67" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C26" s="67" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D26" s="67" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E26" s="67"/>
       <c r="F26" s="67"/>
@@ -14181,7 +14189,7 @@
       <c r="E27" s="67"/>
       <c r="F27" s="67"/>
       <c r="G27" s="67" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H27" s="67"/>
     </row>
@@ -14190,19 +14198,19 @@
         <v>158</v>
       </c>
       <c r="B28" s="67" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C28" s="67" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D28" s="67" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E28" s="67"/>
       <c r="F28" s="67"/>
       <c r="G28" s="67"/>
       <c r="H28" s="67" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14210,19 +14218,19 @@
         <v>158</v>
       </c>
       <c r="B29" s="67" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C29" s="67" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D29" s="67" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E29" s="67"/>
       <c r="F29" s="67"/>
       <c r="G29" s="67"/>
       <c r="H29" s="67" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14230,19 +14238,19 @@
         <v>158</v>
       </c>
       <c r="B30" s="67" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C30" s="67" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D30" s="67" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="E30" s="67"/>
       <c r="F30" s="67"/>
       <c r="G30" s="67"/>
       <c r="H30" s="67" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14250,19 +14258,19 @@
         <v>158</v>
       </c>
       <c r="B31" s="67" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C31" s="67" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D31" s="67" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="E31" s="67"/>
       <c r="F31" s="67"/>
       <c r="G31" s="67"/>
       <c r="H31" s="67" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14270,19 +14278,19 @@
         <v>158</v>
       </c>
       <c r="B32" s="67" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C32" s="67" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D32" s="67" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E32" s="67"/>
       <c r="F32" s="67"/>
       <c r="G32" s="67"/>
       <c r="H32" s="67" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14290,13 +14298,13 @@
         <v>158</v>
       </c>
       <c r="B33" s="67" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C33" s="67" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D33" s="67" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E33" s="67"/>
       <c r="F33" s="67"/>
@@ -14324,20 +14332,20 @@
         <v>164</v>
       </c>
       <c r="B35" s="67" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C35" s="67" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D35" s="67" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="E35" s="67"/>
       <c r="F35" s="67"/>
       <c r="G35" s="67"/>
       <c r="H35" s="67"/>
       <c r="I35" s="64" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14345,20 +14353,20 @@
         <v>164</v>
       </c>
       <c r="B36" s="67" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C36" s="67" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D36" s="67" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E36" s="67"/>
       <c r="F36" s="67"/>
       <c r="G36" s="67"/>
       <c r="H36" s="67"/>
       <c r="I36" s="64" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14366,20 +14374,20 @@
         <v>164</v>
       </c>
       <c r="B37" s="67" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C37" s="67" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D37" s="67" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E37" s="67"/>
       <c r="F37" s="67"/>
       <c r="G37" s="67"/>
       <c r="H37" s="67"/>
       <c r="I37" s="64" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14387,20 +14395,20 @@
         <v>164</v>
       </c>
       <c r="B38" s="67" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C38" s="67" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D38" s="67" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="E38" s="67"/>
       <c r="F38" s="67"/>
       <c r="G38" s="67"/>
       <c r="H38" s="67"/>
       <c r="I38" s="64" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14408,20 +14416,20 @@
         <v>164</v>
       </c>
       <c r="B39" s="67" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C39" s="67" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D39" s="67" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E39" s="67"/>
       <c r="F39" s="67"/>
       <c r="G39" s="67"/>
       <c r="H39" s="67"/>
       <c r="I39" s="64" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14429,19 +14437,19 @@
         <v>164</v>
       </c>
       <c r="B40" s="67" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C40" s="67" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D40" s="67" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E40" s="67"/>
       <c r="F40" s="67"/>
       <c r="G40" s="67"/>
       <c r="H40" s="67" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14449,13 +14457,13 @@
         <v>164</v>
       </c>
       <c r="B41" s="67" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C41" s="67" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D41" s="67" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E41" s="67"/>
       <c r="F41" s="67"/>
@@ -14467,13 +14475,13 @@
         <v>164</v>
       </c>
       <c r="B42" s="67" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C42" s="67" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D42" s="67" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E42" s="67"/>
       <c r="F42" s="67"/>
@@ -14485,13 +14493,13 @@
         <v>164</v>
       </c>
       <c r="B43" s="69" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C43" s="67" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D43" s="67" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E43" s="67"/>
       <c r="F43" s="67"/>
@@ -14503,13 +14511,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="67" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C44" s="67" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D44" s="67" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E44" s="67"/>
       <c r="F44" s="67"/>
@@ -14521,13 +14529,13 @@
         <v>164</v>
       </c>
       <c r="B45" s="67" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C45" s="67" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D45" s="67" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E45" s="67"/>
       <c r="F45" s="67"/>
@@ -14542,10 +14550,10 @@
         <v>163</v>
       </c>
       <c r="C46" s="67" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D46" s="67" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E46" s="67"/>
       <c r="F46" s="67"/>
@@ -14557,13 +14565,13 @@
         <v>164</v>
       </c>
       <c r="B47" s="67" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C47" s="67" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D47" s="67" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E47" s="67"/>
       <c r="F47" s="67"/>
@@ -14580,7 +14588,7 @@
       <c r="E48" s="67"/>
       <c r="F48" s="67"/>
       <c r="G48" s="67" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H48" s="67"/>
     </row>
@@ -14589,13 +14597,13 @@
         <v>200</v>
       </c>
       <c r="B49" s="67" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C49" s="67" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D49" s="67" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E49" s="67"/>
       <c r="F49" s="67"/>
@@ -14607,13 +14615,13 @@
         <v>200</v>
       </c>
       <c r="B50" s="67" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C50" s="67" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D50" s="67" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E50" s="67"/>
       <c r="F50" s="67"/>
@@ -14630,7 +14638,7 @@
       <c r="E51" s="67"/>
       <c r="F51" s="67"/>
       <c r="G51" s="67" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H51" s="67"/>
     </row>
@@ -14639,13 +14647,13 @@
         <v>208</v>
       </c>
       <c r="B52" s="67" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C52" s="67" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D52" s="67" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E52" s="67"/>
       <c r="F52" s="67"/>
@@ -14657,13 +14665,13 @@
         <v>208</v>
       </c>
       <c r="B53" s="67" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C53" s="67" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D53" s="67" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E53" s="67"/>
       <c r="F53" s="67"/>
@@ -14675,13 +14683,13 @@
         <v>208</v>
       </c>
       <c r="B54" s="67" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C54" s="67" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D54" s="67" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E54" s="67"/>
       <c r="F54" s="67"/>
@@ -14693,13 +14701,13 @@
         <v>208</v>
       </c>
       <c r="B55" s="67" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C55" s="67" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D55" s="67" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E55" s="67"/>
       <c r="F55" s="67"/>
@@ -14711,13 +14719,13 @@
         <v>208</v>
       </c>
       <c r="B56" s="67" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C56" s="67" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D56" s="67" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E56" s="67"/>
       <c r="F56" s="67"/>
@@ -14729,13 +14737,13 @@
         <v>224</v>
       </c>
       <c r="B57" s="64" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D57" s="64" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14743,13 +14751,13 @@
         <v>224</v>
       </c>
       <c r="B58" s="64" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C58" s="64" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D58" s="64" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14757,27 +14765,27 @@
         <v>224</v>
       </c>
       <c r="B59" s="64" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C59" s="64" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D59" s="64" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="60" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="68" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B60" s="64" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C60" s="64" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D60" s="64" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E60" s="64"/>
       <c r="F60" s="64"/>
@@ -14787,16 +14795,16 @@
     </row>
     <row r="61" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="68" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B61" s="64" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C61" s="64" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D61" s="64" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E61" s="64"/>
       <c r="F61" s="64"/>
@@ -14806,16 +14814,16 @@
     </row>
     <row r="62" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="68" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B62" s="64" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D62" s="64" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E62" s="64"/>
       <c r="F62" s="64"/>
@@ -14825,16 +14833,16 @@
     </row>
     <row r="63" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="68" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B63" s="64" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C63" s="64" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E63" s="64"/>
       <c r="F63" s="64"/>
@@ -14844,16 +14852,16 @@
     </row>
     <row r="64" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="67" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B64" s="67" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C64" s="46" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="E64" s="46"/>
       <c r="F64" s="46"/>
@@ -14863,16 +14871,16 @@
     </row>
     <row r="65" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="67" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B65" s="67" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C65" s="46" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E65" s="46"/>
       <c r="F65" s="46"/>
@@ -14882,16 +14890,16 @@
     </row>
     <row r="66" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="67" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B66" s="67" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C66" s="46" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="E66" s="46"/>
       <c r="F66" s="46"/>
@@ -14901,16 +14909,16 @@
     </row>
     <row r="67" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="67" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B67" s="67" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C67" s="46" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E67" s="46"/>
       <c r="F67" s="46"/>
@@ -14920,16 +14928,16 @@
     </row>
     <row r="68" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="67" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B68" s="67" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C68" s="46" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E68" s="46"/>
       <c r="F68" s="46"/>
@@ -14939,16 +14947,16 @@
     </row>
     <row r="69" s="2" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="67" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B69" s="67" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C69" s="46" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="E69" s="46"/>
       <c r="F69" s="46"/>
@@ -14958,16 +14966,16 @@
     </row>
     <row r="70" s="2" customFormat="true" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="67" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B70" s="67" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C70" s="46" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="E70" s="46"/>
       <c r="F70" s="46"/>
@@ -14977,16 +14985,16 @@
     </row>
     <row r="71" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="67" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B71" s="67" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C71" s="46" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E71" s="46"/>
       <c r="F71" s="46"/>
@@ -14996,16 +15004,16 @@
     </row>
     <row r="72" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="67" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B72" s="67" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C72" s="46" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="E72" s="46"/>
       <c r="F72" s="46"/>
@@ -15015,16 +15023,16 @@
     </row>
     <row r="73" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="67" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B73" s="67" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C73" s="46" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="E73" s="46"/>
       <c r="F73" s="46"/>
@@ -15034,16 +15042,16 @@
     </row>
     <row r="74" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="67" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B74" s="67" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C74" s="46" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E74" s="46"/>
       <c r="F74" s="46"/>
@@ -15053,58 +15061,58 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="70" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B75" s="69" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C75" s="64" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D75" s="64" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="70" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C76" s="64" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D76" s="64" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="70" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B77" s="64" t="s">
         <v>163</v>
       </c>
       <c r="C77" s="64" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D77" s="64" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="70" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B78" s="64" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C78" s="69" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D78" s="69" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="E78" s="69"/>
       <c r="F78" s="69"/>
@@ -15114,16 +15122,16 @@
         <v>324</v>
       </c>
       <c r="B79" s="64" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C79" s="72" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D79" s="64" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H79" s="69" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15131,13 +15139,13 @@
         <v>324</v>
       </c>
       <c r="B80" s="64" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C80" s="69" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D80" s="72" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="E80" s="72"/>
       <c r="F80" s="72"/>
@@ -15150,13 +15158,13 @@
         <v>324</v>
       </c>
       <c r="B81" s="64" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C81" s="69" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="D81" s="64" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15164,13 +15172,13 @@
         <v>324</v>
       </c>
       <c r="B82" s="64" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C82" s="69" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D82" s="69" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E82" s="69"/>
       <c r="F82" s="69"/>
@@ -15180,13 +15188,13 @@
         <v>324</v>
       </c>
       <c r="B83" s="64" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C83" s="69" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="D83" s="69" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="E83" s="69"/>
       <c r="F83" s="69"/>
@@ -15196,13 +15204,13 @@
         <v>324</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C84" s="69" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="D84" s="69" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="E84" s="69"/>
       <c r="F84" s="69"/>
@@ -15215,13 +15223,13 @@
         <v>324</v>
       </c>
       <c r="B85" s="64" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C85" s="69" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="D85" s="69" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="E85" s="69"/>
       <c r="F85" s="69"/>
@@ -15231,13 +15239,13 @@
         <v>324</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C86" s="69" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D86" s="69" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="E86" s="69"/>
       <c r="F86" s="69"/>
@@ -15253,276 +15261,276 @@
         <v>163</v>
       </c>
       <c r="C87" s="69" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D87" s="64" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="71" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B88" s="64" t="s">
         <v>26</v>
       </c>
       <c r="C88" s="64" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D88" s="64" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="71" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B89" s="64" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C89" s="64" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D89" s="64" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H89" s="64" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="71" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B90" s="64" t="s">
         <v>163</v>
       </c>
       <c r="C90" s="64" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D90" s="64" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="71" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B91" s="69" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C91" s="69" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D91" s="69" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="E91" s="69" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F91" s="69" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H91" s="64" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="71" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B92" s="64" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C92" s="69" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D92" s="69" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="E92" s="69" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F92" s="69" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="71" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B93" s="64" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C93" s="69" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D93" s="69" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E93" s="69" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F93" s="69" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="71" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B94" s="64" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C94" s="64" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D94" s="64" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="71" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B95" s="69" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C95" s="69" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D95" s="69" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="71" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B96" s="69" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C96" s="69" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="D96" s="69" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="71" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B97" s="69" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C97" s="69" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D97" s="69" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="71" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B98" s="69" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C98" s="69" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="D98" s="69" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="71" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G99" s="67" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="71" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G100" s="67" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="71" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B101" s="69" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C101" s="69" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D101" s="69" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="71" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B102" s="69" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C102" s="69" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D102" s="69" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="71" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B103" s="69" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C103" s="69" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D103" s="69" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="71" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B104" s="69" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C104" s="69" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D104" s="69" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="71" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G105" s="67" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="71" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G106" s="67" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15530,13 +15538,13 @@
         <v>177</v>
       </c>
       <c r="B107" s="69" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C107" s="64" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D107" s="64" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15544,13 +15552,13 @@
         <v>177</v>
       </c>
       <c r="B108" s="64" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C108" s="64" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D108" s="64" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15558,13 +15566,13 @@
         <v>177</v>
       </c>
       <c r="B109" s="69" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C109" s="64" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="D109" s="64" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15572,13 +15580,13 @@
         <v>177</v>
       </c>
       <c r="B110" s="69" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C110" s="64" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D110" s="64" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15586,13 +15594,13 @@
         <v>177</v>
       </c>
       <c r="B111" s="69" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C111" s="64" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D111" s="64" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15600,13 +15608,13 @@
         <v>177</v>
       </c>
       <c r="B112" s="69" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C112" s="64" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D112" s="64" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15614,108 +15622,125 @@
         <v>177</v>
       </c>
       <c r="G113" s="67" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="68" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B114" s="67" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C114" s="67" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D114" s="67" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E114" s="67" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F114" s="67" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G114" s="68"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="68" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B115" s="67" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C115" s="67" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D115" s="67" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E115" s="67" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F115" s="67" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="68" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B116" s="67" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C116" s="67" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D116" s="67" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="E116" s="67" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F116" s="67" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="68" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B117" s="67" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C117" s="67" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D117" s="67" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="E117" s="67" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F117" s="67" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="68" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B118" s="67" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C118" s="67" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D118" s="67" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E118" s="67" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F118" s="67" t="s">
-        <v>1001</v>
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="30" t="s">
+        <v>467</v>
+      </c>
+      <c r="B119" s="64" t="s">
+        <v>758</v>
+      </c>
+      <c r="C119" s="64" t="s">
+        <v>759</v>
+      </c>
+      <c r="D119" s="64" t="s">
+        <v>887</v>
+      </c>
+      <c r="H119" s="64" t="s">
+        <v>1003</v>
       </c>
     </row>
     <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -15758,63 +15783,63 @@
   <sheetData>
     <row r="1" s="75" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="74" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B1" s="74" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C1" s="74" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D1" s="74" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="E1" s="74" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="F1" s="74" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="G1" s="74" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="H1" s="74" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="I1" s="74" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="J1" s="74" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="K1" s="74" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="L1" s="75" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="46" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="E2" s="46" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="F2" s="46" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="G2" s="46" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="H2" s="46" t="n">
         <v>-10</v>
@@ -15823,36 +15848,36 @@
         <v>100</v>
       </c>
       <c r="J2" s="46" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="K2" s="46" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="L2" s="46" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="46" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="D3" s="76" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="E3" s="76" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="F3" s="76" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="G3" s="46" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="H3" s="46" t="n">
         <v>-10</v>
@@ -15861,36 +15886,36 @@
         <v>100</v>
       </c>
       <c r="J3" s="46" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="K3" s="46" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="L3" s="46" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="46" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="G4" s="46" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="H4" s="46" t="n">
         <v>-10</v>
@@ -15899,36 +15924,36 @@
         <v>100</v>
       </c>
       <c r="J4" s="46" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="K4" s="46" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="L4" s="46" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="46" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="F5" s="46" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="G5" s="46" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="H5" s="46" t="n">
         <v>-10</v>
@@ -15937,13 +15962,13 @@
         <v>100</v>
       </c>
       <c r="J5" s="46" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="K5" s="46" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="L5" s="46" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -15974,10 +15999,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>6</v>
@@ -15997,13 +16022,13 @@
         <v>107</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -16013,13 +16038,13 @@
         <v>107</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -16029,13 +16054,13 @@
         <v>428</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="E4" s="10"/>
     </row>
@@ -16044,13 +16069,13 @@
         <v>428</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16058,13 +16083,13 @@
         <v>428</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16072,13 +16097,13 @@
         <v>428</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16086,13 +16111,13 @@
         <v>428</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16100,13 +16125,13 @@
         <v>428</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16114,13 +16139,13 @@
         <v>428</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16128,13 +16153,13 @@
         <v>428</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16142,13 +16167,13 @@
         <v>428</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16156,13 +16181,13 @@
         <v>428</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16170,13 +16195,13 @@
         <v>428</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16184,13 +16209,13 @@
         <v>428</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16198,19 +16223,19 @@
         <v>332</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16218,19 +16243,19 @@
         <v>332</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16238,19 +16263,19 @@
         <v>332</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16258,19 +16283,19 @@
         <v>332</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16278,19 +16303,19 @@
         <v>332</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16298,13 +16323,13 @@
         <v>332</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16312,13 +16337,13 @@
         <v>332</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16326,13 +16351,13 @@
         <v>332</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16340,13 +16365,13 @@
         <v>332</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16354,19 +16379,19 @@
         <v>332</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16374,13 +16399,13 @@
         <v>332</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16388,13 +16413,13 @@
         <v>332</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16402,13 +16427,13 @@
         <v>332</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16416,13 +16441,13 @@
         <v>332</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16430,13 +16455,13 @@
         <v>332</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16444,13 +16469,13 @@
         <v>332</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16458,13 +16483,13 @@
         <v>332</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16472,13 +16497,13 @@
         <v>332</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16486,13 +16511,13 @@
         <v>332</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16500,13 +16525,13 @@
         <v>332</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16514,13 +16539,13 @@
         <v>332</v>
       </c>
       <c r="B36" s="10" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>1153</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>1151</v>
-      </c>
       <c r="D36" s="10" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16528,13 +16553,13 @@
         <v>332</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16542,13 +16567,13 @@
         <v>332</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16556,13 +16581,13 @@
         <v>332</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16570,13 +16595,13 @@
         <v>332</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16584,13 +16609,13 @@
         <v>332</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16598,13 +16623,13 @@
         <v>332</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16612,13 +16637,13 @@
         <v>332</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16626,13 +16651,13 @@
         <v>332</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16640,13 +16665,13 @@
         <v>332</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16654,13 +16679,13 @@
         <v>332</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16668,19 +16693,19 @@
         <v>332</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16688,19 +16713,19 @@
         <v>332</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16708,19 +16733,19 @@
         <v>332</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16728,19 +16753,19 @@
         <v>332</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16748,19 +16773,19 @@
         <v>332</v>
       </c>
       <c r="B51" s="46" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16768,19 +16793,19 @@
         <v>332</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16788,19 +16813,19 @@
         <v>332</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16808,13 +16833,13 @@
         <v>107</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16822,13 +16847,13 @@
         <v>107</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16836,13 +16861,13 @@
         <v>107</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16850,13 +16875,13 @@
         <v>107</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16864,13 +16889,13 @@
         <v>107</v>
       </c>
       <c r="B58" s="77" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16878,13 +16903,13 @@
         <v>107</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16892,13 +16917,13 @@
         <v>107</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16906,19 +16931,19 @@
         <v>107</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16926,13 +16951,13 @@
         <v>107</v>
       </c>
       <c r="B62" s="35" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="C62" s="35" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="D62" s="77" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
@@ -16942,13 +16967,13 @@
         <v>107</v>
       </c>
       <c r="B63" s="35" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="C63" s="35" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="D63" s="77" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
@@ -16958,13 +16983,13 @@
         <v>107</v>
       </c>
       <c r="B64" s="35" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="C64" s="35" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="D64" s="77" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
@@ -16974,13 +16999,13 @@
         <v>332</v>
       </c>
       <c r="B65" s="61" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="C65" s="61" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D65" s="61" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E65" s="61"/>
       <c r="F65" s="61"/>
@@ -16990,13 +17015,13 @@
         <v>332</v>
       </c>
       <c r="B66" s="61" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C66" s="61" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D66" s="61" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="E66" s="61"/>
       <c r="F66" s="61"/>
@@ -17006,13 +17031,13 @@
         <v>332</v>
       </c>
       <c r="B67" s="61" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="C67" s="61" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D67" s="61" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="E67" s="61"/>
       <c r="F67" s="61"/>
@@ -17022,19 +17047,19 @@
         <v>332</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17042,19 +17067,19 @@
         <v>428</v>
       </c>
       <c r="B69" s="61" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17062,19 +17087,19 @@
         <v>428</v>
       </c>
       <c r="B70" s="61" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17082,13 +17107,13 @@
         <v>428</v>
       </c>
       <c r="B71" s="61" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="E71" s="10"/>
       <c r="F71" s="10"/>
@@ -17098,13 +17123,13 @@
         <v>428</v>
       </c>
       <c r="B72" s="61" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="E72" s="10"/>
       <c r="F72" s="10"/>
@@ -17114,13 +17139,13 @@
         <v>428</v>
       </c>
       <c r="B73" s="61" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="E73" s="10"/>
       <c r="F73" s="10"/>
@@ -17130,13 +17155,13 @@
         <v>428</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="E74" s="10"/>
       <c r="F74" s="10"/>
@@ -17146,13 +17171,13 @@
         <v>332</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17160,13 +17185,13 @@
         <v>332</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17174,13 +17199,13 @@
         <v>332</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17188,13 +17213,13 @@
         <v>332</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17202,19 +17227,19 @@
         <v>107</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17222,19 +17247,19 @@
         <v>107</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17242,19 +17267,19 @@
         <v>107</v>
       </c>
       <c r="B81" s="20" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17262,19 +17287,19 @@
         <v>107</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17282,19 +17307,19 @@
         <v>107</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17302,19 +17327,19 @@
         <v>281</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17322,33 +17347,33 @@
         <v>281</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17356,13 +17381,13 @@
         <v>428</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17370,13 +17395,13 @@
         <v>428</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17384,13 +17409,13 @@
         <v>428</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17398,13 +17423,13 @@
         <v>428</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17412,13 +17437,13 @@
         <v>428</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17426,13 +17451,13 @@
         <v>428</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17440,13 +17465,13 @@
         <v>428</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17454,13 +17479,13 @@
         <v>428</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17468,13 +17493,13 @@
         <v>428</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17482,13 +17507,13 @@
         <v>428</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17496,13 +17521,13 @@
         <v>428</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17510,13 +17535,13 @@
         <v>428</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17524,13 +17549,13 @@
         <v>428</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17538,13 +17563,13 @@
         <v>428</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17552,13 +17577,13 @@
         <v>428</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17566,13 +17591,13 @@
         <v>428</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17580,13 +17605,13 @@
         <v>428</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17594,13 +17619,13 @@
         <v>428</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17608,13 +17633,13 @@
         <v>428</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17622,13 +17647,13 @@
         <v>428</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17636,13 +17661,13 @@
         <v>428</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17650,13 +17675,13 @@
         <v>428</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17664,13 +17689,13 @@
         <v>428</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17678,13 +17703,13 @@
         <v>428</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17692,13 +17717,13 @@
         <v>428</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17706,13 +17731,13 @@
         <v>428</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17720,13 +17745,13 @@
         <v>428</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17734,13 +17759,13 @@
         <v>428</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17748,13 +17773,13 @@
         <v>428</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
@@ -17764,13 +17789,13 @@
         <v>428</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
@@ -17780,13 +17805,13 @@
         <v>428</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
@@ -17796,13 +17821,13 @@
         <v>428</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
@@ -17812,13 +17837,13 @@
         <v>428</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
@@ -17828,13 +17853,13 @@
         <v>428</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
@@ -17844,13 +17869,13 @@
         <v>428</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
@@ -17860,13 +17885,13 @@
         <v>428</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
@@ -17876,13 +17901,13 @@
         <v>428</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
@@ -17892,13 +17917,13 @@
         <v>428</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
@@ -17908,13 +17933,13 @@
         <v>428</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
@@ -17924,13 +17949,13 @@
         <v>428</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
@@ -17940,13 +17965,13 @@
         <v>428</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
@@ -17956,13 +17981,13 @@
         <v>428</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
@@ -17972,13 +17997,13 @@
         <v>428</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
@@ -17988,13 +18013,13 @@
         <v>428</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
@@ -18004,13 +18029,13 @@
         <v>428</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
@@ -18020,13 +18045,13 @@
         <v>428</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
@@ -18036,13 +18061,13 @@
         <v>428</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
@@ -18052,13 +18077,13 @@
         <v>428</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
@@ -18068,13 +18093,13 @@
         <v>428</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
@@ -18084,13 +18109,13 @@
         <v>428</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
@@ -18100,13 +18125,13 @@
         <v>428</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
@@ -18116,13 +18141,13 @@
         <v>428</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
@@ -18132,13 +18157,13 @@
         <v>428</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
@@ -18148,13 +18173,13 @@
         <v>428</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
@@ -18164,13 +18189,13 @@
         <v>428</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
@@ -18180,13 +18205,13 @@
         <v>428</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
@@ -18196,13 +18221,13 @@
         <v>428</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
